--- a/scripts/generate_report_from_webgains/enriched_webgains_reports/Transacciones_newcop_2510_enriched.xlsx
+++ b/scripts/generate_report_from_webgains/enriched_webgains_reports/Transacciones_newcop_2510_enriched.xlsx
@@ -657,7 +657,7 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Reventa</t>
+          <t>Retail</t>
         </is>
       </c>
       <c r="B11" s="4" t="n">
@@ -665,22 +665,22 @@
       </c>
       <c r="C11" s="4" t="inlineStr">
         <is>
-          <t>61.90%</t>
+          <t>60.94%</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Retail</t>
+          <t>Resell</t>
         </is>
       </c>
       <c r="B12" s="4" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="C12" s="4" t="inlineStr">
         <is>
-          <t>38.10%</t>
+          <t>39.06%</t>
         </is>
       </c>
     </row>
@@ -691,7 +691,7 @@
         </is>
       </c>
       <c r="B13" s="6" t="n">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="C13" s="6" t="inlineStr">
         <is>
@@ -900,7 +900,7 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Puma LaMelo Ball LaFrancé Amour Moment</t>
+          <t>Air Jordan 11 Retro Cherry (2022)</t>
         </is>
       </c>
       <c r="B30" s="4" t="n">
@@ -915,7 +915,7 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Air Jordan 11 Retro Cherry (2022)</t>
+          <t>Puma LaMelo Ball LaFrancé Amour Moment</t>
         </is>
       </c>
       <c r="B31" s="4" t="n">
@@ -1020,7 +1020,7 @@
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>Fakegods Valentines Hoodie Black</t>
+          <t>Air Jordan 3 Retro Pure Money</t>
         </is>
       </c>
       <c r="B38" s="4" t="n">
@@ -1035,7 +1035,7 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>Air Jordan 3 Retro Pure Money</t>
+          <t>Fakegods Valentines Hoodie Black</t>
         </is>
       </c>
       <c r="B39" s="4" t="n">
@@ -1236,53 +1236,53 @@
     <row r="51">
       <c r="A51" s="8" t="inlineStr">
         <is>
-          <t>80587</t>
-        </is>
-      </c>
-      <c r="B51" s="14" t="inlineStr">
-        <is>
-          <t>PEDIDO NO PREPARADO</t>
+          <t>80603</t>
+        </is>
+      </c>
+      <c r="B51" s="9" t="inlineStr">
+        <is>
+          <t>Issue (PARTIALLY REFUNDED)</t>
         </is>
       </c>
       <c r="C51" s="10" t="inlineStr">
         <is>
-          <t>EXPIRED</t>
+          <t>PARTIALLY_REFUNDED</t>
         </is>
       </c>
       <c r="D51" s="10" t="inlineStr">
         <is>
-          <t>UNFULFILLED</t>
-        </is>
-      </c>
-      <c r="E51" s="10" t="inlineStr"/>
+          <t>FULFILLED</t>
+        </is>
+      </c>
+      <c r="E51" s="11" t="inlineStr">
+        <is>
+          <t>79.00 EUR / 79.00 EUR</t>
+        </is>
+      </c>
       <c r="F51" s="10" t="inlineStr"/>
     </row>
     <row r="52">
       <c r="A52" s="8" t="inlineStr">
         <is>
-          <t>80603</t>
-        </is>
-      </c>
-      <c r="B52" s="9" t="inlineStr">
-        <is>
-          <t>Issue (PARTIALLY REFUNDED)</t>
+          <t>80587</t>
+        </is>
+      </c>
+      <c r="B52" s="14" t="inlineStr">
+        <is>
+          <t>PEDIDO NO PREPARADO</t>
         </is>
       </c>
       <c r="C52" s="10" t="inlineStr">
         <is>
-          <t>PARTIALLY_REFUNDED</t>
+          <t>EXPIRED</t>
         </is>
       </c>
       <c r="D52" s="10" t="inlineStr">
         <is>
-          <t>FULFILLED</t>
-        </is>
-      </c>
-      <c r="E52" s="11" t="inlineStr">
-        <is>
-          <t>79.00 EUR / 79.00 EUR</t>
-        </is>
-      </c>
+          <t>UNFULFILLED</t>
+        </is>
+      </c>
+      <c r="E52" s="10" t="inlineStr"/>
       <c r="F52" s="10" t="inlineStr"/>
     </row>
     <row r="53">
@@ -1618,26 +1618,26 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Invoke AB</t>
+          <t>Shoparize</t>
         </is>
       </c>
       <c r="B2" s="16" t="n">
-        <v>79</v>
+        <v>110</v>
       </c>
       <c r="C2" s="16" t="n">
-        <v>3.95</v>
+        <v>5.5</v>
       </c>
       <c r="D2" s="16" t="n">
-        <v>1.19</v>
+        <v>1.65</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>10/31/25 17:34</t>
+          <t>10/31/25 20:32</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>82052</t>
+          <t>82087</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
@@ -1657,17 +1657,17 @@
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>Fakegods Valentines Hoodie Black</t>
+          <t>Adidas Handball Spezial Earth Strata Gum</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>38.6 EU - 6 US</t>
         </is>
       </c>
       <c r="L2" t="inlineStr">
         <is>
-          <t>valentineb</t>
+          <t>IF6490</t>
         </is>
       </c>
       <c r="M2" t="inlineStr">
@@ -1691,42 +1691,54 @@
       <c r="S2" t="inlineStr"/>
       <c r="T2" t="inlineStr">
         <is>
-          <t>edigamboy1905@gmail.com</t>
+          <t>laessu@hotmail.com</t>
         </is>
       </c>
       <c r="U2" t="inlineStr">
         <is>
-          <t>Ediver</t>
+          <t>Laura</t>
         </is>
       </c>
       <c r="V2" t="inlineStr">
         <is>
-          <t>Gamboy</t>
+          <t>Suárez Vera</t>
         </is>
       </c>
       <c r="W2" t="inlineStr">
         <is>
-          <t>+34611511452</t>
+          <t>+34617598662</t>
         </is>
       </c>
       <c r="X2" t="inlineStr">
         <is>
-          <t>Repeat Customer (Order #3)</t>
+          <t>Repeat Customer (Order #2)</t>
         </is>
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>direct</t>
-        </is>
-      </c>
-      <c r="AA2" t="inlineStr"/>
-      <c r="AB2" t="inlineStr"/>
-      <c r="AC2" t="inlineStr"/>
+          <t>Google</t>
+        </is>
+      </c>
+      <c r="AA2" t="inlineStr">
+        <is>
+          <t>google</t>
+        </is>
+      </c>
+      <c r="AB2" t="inlineStr">
+        <is>
+          <t>cpc</t>
+        </is>
+      </c>
+      <c r="AC2" t="inlineStr">
+        <is>
+          <t>{campaignname}</t>
+        </is>
+      </c>
       <c r="AD2" t="inlineStr"/>
       <c r="AE2" t="inlineStr"/>
       <c r="AF2" t="inlineStr"/>
@@ -1862,26 +1874,26 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Pashion.dk ApS</t>
+          <t>Invoke AB</t>
         </is>
       </c>
       <c r="B4" s="16" t="n">
-        <v>220</v>
+        <v>79</v>
       </c>
       <c r="C4" s="16" t="n">
-        <v>13.2</v>
+        <v>3.95</v>
       </c>
       <c r="D4" s="16" t="n">
-        <v>3.96</v>
+        <v>1.19</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>10/30/25 15:27</t>
+          <t>10/31/25 17:34</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>81940</t>
+          <t>82052</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
@@ -1891,27 +1903,27 @@
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>Reventa</t>
+          <t>Retail</t>
         </is>
       </c>
       <c r="I4" s="17" t="inlineStr">
         <is>
-          <t>6%</t>
+          <t>5%</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>Nike Air Force 1 Low Supreme Black White</t>
+          <t>Fakegods Valentines Hoodie Black</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
         <is>
-          <t>40 EU - 7 US</t>
+          <t>M</t>
         </is>
       </c>
       <c r="L4" t="inlineStr">
         <is>
-          <t>CU9225-002</t>
+          <t>valentineb</t>
         </is>
       </c>
       <c r="M4" t="inlineStr">
@@ -1935,32 +1947,32 @@
       <c r="S4" t="inlineStr"/>
       <c r="T4" t="inlineStr">
         <is>
-          <t>adrireke86@gmail.com</t>
+          <t>edigamboy1905@gmail.com</t>
         </is>
       </c>
       <c r="U4" t="inlineStr">
         <is>
-          <t>Adrian</t>
+          <t>Ediver</t>
         </is>
       </c>
       <c r="V4" t="inlineStr">
         <is>
-          <t>Requena tellado</t>
+          <t>Gamboy</t>
         </is>
       </c>
       <c r="W4" t="inlineStr">
         <is>
-          <t>+34676637620</t>
+          <t>+34611511452</t>
         </is>
       </c>
       <c r="X4" t="inlineStr">
         <is>
-          <t>Repeat Customer (Order #3)</t>
+          <t>Repeat Customer (Order #4)</t>
         </is>
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
@@ -1978,26 +1990,26 @@
     <row r="5">
       <c r="A5" s="18" t="inlineStr">
         <is>
-          <t>Shoparize</t>
+          <t>Pashion.dk ApS</t>
         </is>
       </c>
       <c r="B5" s="19" t="n">
-        <v>110</v>
+        <v>72</v>
       </c>
       <c r="C5" s="19" t="n">
-        <v>5.5</v>
+        <v>4.32</v>
       </c>
       <c r="D5" s="19" t="n">
-        <v>1.65</v>
+        <v>1.3</v>
       </c>
       <c r="E5" s="18" t="inlineStr">
         <is>
-          <t>10/31/25 20:32</t>
+          <t>10/30/25 17:45</t>
         </is>
       </c>
       <c r="F5" s="18" t="inlineStr">
         <is>
-          <t>82087</t>
+          <t>81967</t>
         </is>
       </c>
       <c r="G5" s="18" t="inlineStr">
@@ -2007,27 +2019,27 @@
       </c>
       <c r="H5" s="18" t="inlineStr">
         <is>
-          <t>Retail</t>
+          <t>Reventa</t>
         </is>
       </c>
       <c r="I5" s="20" t="inlineStr">
         <is>
-          <t>5%</t>
+          <t>6%</t>
         </is>
       </c>
       <c r="J5" s="18" t="inlineStr">
         <is>
-          <t>Adidas Handball Spezial Earth Strata Gum</t>
+          <t>Adidas Samba OG Grey Two</t>
         </is>
       </c>
       <c r="K5" s="18" t="inlineStr">
         <is>
-          <t>38.6 EU - 6 US</t>
+          <t>40 EU - 7 US</t>
         </is>
       </c>
       <c r="L5" s="18" t="inlineStr">
         <is>
-          <t>IF6490</t>
+          <t>JI3207</t>
         </is>
       </c>
       <c r="M5" s="18" t="inlineStr">
@@ -2051,32 +2063,28 @@
       <c r="S5" s="18" t="inlineStr"/>
       <c r="T5" s="18" t="inlineStr">
         <is>
-          <t>laessu@hotmail.com</t>
+          <t>ferreiramiguezsusana@gmail.com</t>
         </is>
       </c>
       <c r="U5" s="18" t="inlineStr">
         <is>
-          <t>Laura</t>
+          <t>Susana</t>
         </is>
       </c>
       <c r="V5" s="18" t="inlineStr">
         <is>
-          <t>Suárez Vera</t>
-        </is>
-      </c>
-      <c r="W5" s="18" t="inlineStr">
-        <is>
-          <t>+34617598662</t>
-        </is>
-      </c>
+          <t>Ferreira Miguez</t>
+        </is>
+      </c>
+      <c r="W5" s="18" t="inlineStr"/>
       <c r="X5" s="18" t="inlineStr">
         <is>
-          <t>Repeat Customer (Order #2)</t>
+          <t>First Order</t>
         </is>
       </c>
       <c r="Y5" s="18" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="Z5" s="18" t="inlineStr">
@@ -2110,22 +2118,22 @@
         </is>
       </c>
       <c r="B6" s="16" t="n">
-        <v>72</v>
+        <v>220</v>
       </c>
       <c r="C6" s="16" t="n">
-        <v>4.32</v>
+        <v>13.2</v>
       </c>
       <c r="D6" s="16" t="n">
-        <v>1.3</v>
+        <v>3.96</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>10/30/25 17:45</t>
+          <t>10/30/25 15:27</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>81967</t>
+          <t>81940</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
@@ -2145,7 +2153,7 @@
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>Adidas Samba OG Grey Two</t>
+          <t>Nike Air Force 1 Low Supreme Black White</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
@@ -2155,7 +2163,7 @@
       </c>
       <c r="L6" t="inlineStr">
         <is>
-          <t>JI3207</t>
+          <t>CU9225-002</t>
         </is>
       </c>
       <c r="M6" t="inlineStr">
@@ -2179,50 +2187,42 @@
       <c r="S6" t="inlineStr"/>
       <c r="T6" t="inlineStr">
         <is>
-          <t>ferreiramiguezsusana@gmail.com</t>
+          <t>adrireke86@gmail.com</t>
         </is>
       </c>
       <c r="U6" t="inlineStr">
         <is>
-          <t>Susana</t>
+          <t>Adrian</t>
         </is>
       </c>
       <c r="V6" t="inlineStr">
         <is>
-          <t>Ferreira Miguez</t>
-        </is>
-      </c>
-      <c r="W6" t="inlineStr"/>
+          <t>Requena tellado</t>
+        </is>
+      </c>
+      <c r="W6" t="inlineStr">
+        <is>
+          <t>+34676637620</t>
+        </is>
+      </c>
       <c r="X6" t="inlineStr">
         <is>
-          <t>First Order</t>
+          <t>Repeat Customer (Order #3)</t>
         </is>
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>3</t>
         </is>
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>Google</t>
-        </is>
-      </c>
-      <c r="AA6" t="inlineStr">
-        <is>
-          <t>google</t>
-        </is>
-      </c>
-      <c r="AB6" t="inlineStr">
-        <is>
-          <t>cpc</t>
-        </is>
-      </c>
-      <c r="AC6" t="inlineStr">
-        <is>
-          <t>{campaignname}</t>
-        </is>
-      </c>
+          <t>direct</t>
+        </is>
+      </c>
+      <c r="AA6" t="inlineStr"/>
+      <c r="AB6" t="inlineStr"/>
+      <c r="AC6" t="inlineStr"/>
       <c r="AD6" t="inlineStr"/>
       <c r="AE6" t="inlineStr"/>
       <c r="AF6" t="inlineStr"/>
@@ -2866,26 +2866,26 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Invoke AB</t>
+          <t>Digital Expand</t>
         </is>
       </c>
       <c r="B12" s="16" t="n">
-        <v>170</v>
+        <v>120</v>
       </c>
       <c r="C12" s="16" t="n">
-        <v>8.5</v>
+        <v>7.2</v>
       </c>
       <c r="D12" s="16" t="n">
-        <v>2.55</v>
+        <v>2.16</v>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>10/27/25 18:02</t>
+          <t>10/27/25 16:56</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>81740</t>
+          <t>81727</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
@@ -2895,27 +2895,27 @@
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>Retail</t>
+          <t>Reventa</t>
         </is>
       </c>
       <c r="I12" s="17" t="inlineStr">
         <is>
-          <t>5%</t>
+          <t>6%</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>Nike Air Force 1 Rope Laces</t>
+          <t>Adidas Samba OG Maroon Off White Gum</t>
         </is>
       </c>
       <c r="K12" t="inlineStr">
         <is>
-          <t>41 EU - 8 US</t>
+          <t>42.6 EU - 9 US</t>
         </is>
       </c>
       <c r="L12" t="inlineStr">
         <is>
-          <t>CW2288-111ME</t>
+          <t>JR8844</t>
         </is>
       </c>
       <c r="M12" t="inlineStr">
@@ -2939,42 +2939,50 @@
       <c r="S12" t="inlineStr"/>
       <c r="T12" t="inlineStr">
         <is>
-          <t>buadeseliane@gmail.com</t>
+          <t>carlosariaspolonio@gmail.com</t>
         </is>
       </c>
       <c r="U12" t="inlineStr">
         <is>
-          <t>Eliane</t>
+          <t>Carlos</t>
         </is>
       </c>
       <c r="V12" t="inlineStr">
         <is>
-          <t>Buades Ruiz</t>
-        </is>
-      </c>
-      <c r="W12" t="inlineStr">
-        <is>
-          <t>+34630180798</t>
-        </is>
-      </c>
+          <t>Arias Polonio</t>
+        </is>
+      </c>
+      <c r="W12" t="inlineStr"/>
       <c r="X12" t="inlineStr">
         <is>
-          <t>First Order</t>
+          <t>Repeat Customer (Order #2)</t>
         </is>
       </c>
       <c r="Y12" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>direct</t>
-        </is>
-      </c>
-      <c r="AA12" t="inlineStr"/>
-      <c r="AB12" t="inlineStr"/>
-      <c r="AC12" t="inlineStr"/>
+          <t>Google</t>
+        </is>
+      </c>
+      <c r="AA12" t="inlineStr">
+        <is>
+          <t>google</t>
+        </is>
+      </c>
+      <c r="AB12" t="inlineStr">
+        <is>
+          <t>cpc</t>
+        </is>
+      </c>
+      <c r="AC12" t="inlineStr">
+        <is>
+          <t>{campaignname}</t>
+        </is>
+      </c>
       <c r="AD12" t="inlineStr"/>
       <c r="AE12" t="inlineStr"/>
       <c r="AF12" t="inlineStr"/>
@@ -2982,26 +2990,26 @@
     <row r="13">
       <c r="A13" s="18" t="inlineStr">
         <is>
-          <t>Purplee Corp</t>
+          <t>Invoke AB</t>
         </is>
       </c>
       <c r="B13" s="19" t="n">
-        <v>82.5</v>
+        <v>170</v>
       </c>
       <c r="C13" s="19" t="n">
-        <v>4.95</v>
+        <v>8.5</v>
       </c>
       <c r="D13" s="19" t="n">
-        <v>1.49</v>
+        <v>2.55</v>
       </c>
       <c r="E13" s="18" t="inlineStr">
         <is>
-          <t>10/28/25 14:36</t>
+          <t>10/27/25 18:02</t>
         </is>
       </c>
       <c r="F13" s="18" t="inlineStr">
         <is>
-          <t>81794</t>
+          <t>81740</t>
         </is>
       </c>
       <c r="G13" s="18" t="inlineStr">
@@ -3011,27 +3019,27 @@
       </c>
       <c r="H13" s="18" t="inlineStr">
         <is>
-          <t>Reventa</t>
+          <t>Retail</t>
         </is>
       </c>
       <c r="I13" s="20" t="inlineStr">
         <is>
-          <t>6%</t>
+          <t>5%</t>
         </is>
       </c>
       <c r="J13" s="18" t="inlineStr">
         <is>
-          <t>Adidas Handball Spezial Maroon Preloved Red Gum</t>
+          <t>Nike Air Force 1 Rope Laces</t>
         </is>
       </c>
       <c r="K13" s="18" t="inlineStr">
         <is>
-          <t>41.3 EU - 8 US</t>
+          <t>41 EU - 8 US</t>
         </is>
       </c>
       <c r="L13" s="18" t="inlineStr">
         <is>
-          <t>JR0848</t>
+          <t>CW2288-111ME</t>
         </is>
       </c>
       <c r="M13" s="18" t="inlineStr">
@@ -3055,20 +3063,24 @@
       <c r="S13" s="18" t="inlineStr"/>
       <c r="T13" s="18" t="inlineStr">
         <is>
-          <t>patxiiraizoza@gmail.com</t>
+          <t>buadeseliane@gmail.com</t>
         </is>
       </c>
       <c r="U13" s="18" t="inlineStr">
         <is>
-          <t>Patxi</t>
+          <t>Eliane</t>
         </is>
       </c>
       <c r="V13" s="18" t="inlineStr">
         <is>
-          <t>Iraizoz Aguerri</t>
-        </is>
-      </c>
-      <c r="W13" s="18" t="inlineStr"/>
+          <t>Buades Ruiz</t>
+        </is>
+      </c>
+      <c r="W13" s="18" t="inlineStr">
+        <is>
+          <t>+34630180798</t>
+        </is>
+      </c>
       <c r="X13" s="18" t="inlineStr">
         <is>
           <t>First Order</t>
@@ -3079,7 +3091,11 @@
           <t>1</t>
         </is>
       </c>
-      <c r="Z13" s="18" t="inlineStr"/>
+      <c r="Z13" s="18" t="inlineStr">
+        <is>
+          <t>direct</t>
+        </is>
+      </c>
       <c r="AA13" s="18" t="inlineStr"/>
       <c r="AB13" s="18" t="inlineStr"/>
       <c r="AC13" s="18" t="inlineStr"/>
@@ -3090,26 +3106,26 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Digital Expand</t>
+          <t>Purplee Corp</t>
         </is>
       </c>
       <c r="B14" s="16" t="n">
-        <v>120</v>
+        <v>82.5</v>
       </c>
       <c r="C14" s="16" t="n">
-        <v>7.2</v>
+        <v>4.95</v>
       </c>
       <c r="D14" s="16" t="n">
-        <v>2.16</v>
+        <v>1.49</v>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>10/27/25 16:56</t>
+          <t>10/28/25 14:36</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>81727</t>
+          <t>81794</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
@@ -3129,17 +3145,17 @@
       </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t>Adidas Samba OG Maroon Off White Gum</t>
+          <t>Adidas Handball Spezial Maroon Preloved Red Gum</t>
         </is>
       </c>
       <c r="K14" t="inlineStr">
         <is>
-          <t>42.6 EU - 9 US</t>
+          <t>41.3 EU - 8 US</t>
         </is>
       </c>
       <c r="L14" t="inlineStr">
         <is>
-          <t>JR8844</t>
+          <t>JR0848</t>
         </is>
       </c>
       <c r="M14" t="inlineStr">
@@ -3163,50 +3179,34 @@
       <c r="S14" t="inlineStr"/>
       <c r="T14" t="inlineStr">
         <is>
-          <t>carlosariaspolonio@gmail.com</t>
+          <t>patxiiraizoza@gmail.com</t>
         </is>
       </c>
       <c r="U14" t="inlineStr">
         <is>
-          <t>Carlos</t>
+          <t>Patxi</t>
         </is>
       </c>
       <c r="V14" t="inlineStr">
         <is>
-          <t>Arias Polonio</t>
+          <t>Iraizoz Aguerri</t>
         </is>
       </c>
       <c r="W14" t="inlineStr"/>
       <c r="X14" t="inlineStr">
         <is>
-          <t>Repeat Customer (Order #2)</t>
+          <t>First Order</t>
         </is>
       </c>
       <c r="Y14" t="inlineStr">
         <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="Z14" t="inlineStr">
-        <is>
-          <t>Google</t>
-        </is>
-      </c>
-      <c r="AA14" t="inlineStr">
-        <is>
-          <t>google</t>
-        </is>
-      </c>
-      <c r="AB14" t="inlineStr">
-        <is>
-          <t>cpc</t>
-        </is>
-      </c>
-      <c r="AC14" t="inlineStr">
-        <is>
-          <t>{campaignname}</t>
-        </is>
-      </c>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="Z14" t="inlineStr"/>
+      <c r="AA14" t="inlineStr"/>
+      <c r="AB14" t="inlineStr"/>
+      <c r="AC14" t="inlineStr"/>
       <c r="AD14" t="inlineStr"/>
       <c r="AE14" t="inlineStr"/>
       <c r="AF14" t="inlineStr"/>
@@ -3454,26 +3454,26 @@
     <row r="17">
       <c r="A17" s="18" t="inlineStr">
         <is>
-          <t>Digital Expand</t>
+          <t>Invoke AB</t>
         </is>
       </c>
       <c r="B17" s="19" t="n">
-        <v>90</v>
+        <v>72</v>
       </c>
       <c r="C17" s="19" t="n">
-        <v>5.4</v>
+        <v>4.32</v>
       </c>
       <c r="D17" s="19" t="n">
-        <v>1.62</v>
+        <v>1.3</v>
       </c>
       <c r="E17" s="18" t="inlineStr">
         <is>
-          <t>10/26/25 18:15</t>
+          <t>10/26/25 01:10</t>
         </is>
       </c>
       <c r="F17" s="18" t="inlineStr">
         <is>
-          <t>81633</t>
+          <t>81554</t>
         </is>
       </c>
       <c r="G17" s="18" t="inlineStr">
@@ -3493,17 +3493,17 @@
       </c>
       <c r="J17" s="18" t="inlineStr">
         <is>
-          <t>Adidas SL 72 OG Maroon Preloved Brown</t>
+          <t>Adidas Samba OG Grey Two</t>
         </is>
       </c>
       <c r="K17" s="18" t="inlineStr">
         <is>
-          <t>39.3 EU - 6.5 US</t>
+          <t>40 EU - 7 US</t>
         </is>
       </c>
       <c r="L17" s="18" t="inlineStr">
         <is>
-          <t>IE3425</t>
+          <t>JI3207</t>
         </is>
       </c>
       <c r="M17" s="18" t="inlineStr">
@@ -3527,17 +3527,17 @@
       <c r="S17" s="18" t="inlineStr"/>
       <c r="T17" s="18" t="inlineStr">
         <is>
-          <t>anamavi79@gmail.com</t>
+          <t>azahara713@hotmail.com</t>
         </is>
       </c>
       <c r="U17" s="18" t="inlineStr">
         <is>
-          <t>ANA</t>
+          <t>PILAR</t>
         </is>
       </c>
       <c r="V17" s="18" t="inlineStr">
         <is>
-          <t>Díaz MORALES</t>
+          <t>Perez</t>
         </is>
       </c>
       <c r="W17" s="18" t="inlineStr"/>
@@ -3578,26 +3578,26 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Invoke AB</t>
+          <t>Digital Expand</t>
         </is>
       </c>
       <c r="B18" s="16" t="n">
-        <v>72</v>
+        <v>90</v>
       </c>
       <c r="C18" s="16" t="n">
-        <v>4.32</v>
+        <v>5.4</v>
       </c>
       <c r="D18" s="16" t="n">
-        <v>1.3</v>
+        <v>1.62</v>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>10/26/25 01:10</t>
+          <t>10/26/25 18:15</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>81554</t>
+          <t>81633</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
@@ -3617,17 +3617,17 @@
       </c>
       <c r="J18" t="inlineStr">
         <is>
-          <t>Adidas Samba OG Grey Two</t>
+          <t>Adidas SL 72 OG Maroon Preloved Brown</t>
         </is>
       </c>
       <c r="K18" t="inlineStr">
         <is>
-          <t>40 EU - 7 US</t>
+          <t>39.3 EU - 6.5 US</t>
         </is>
       </c>
       <c r="L18" t="inlineStr">
         <is>
-          <t>JI3207</t>
+          <t>IE3425</t>
         </is>
       </c>
       <c r="M18" t="inlineStr">
@@ -3651,17 +3651,17 @@
       <c r="S18" t="inlineStr"/>
       <c r="T18" t="inlineStr">
         <is>
-          <t>azahara713@hotmail.com</t>
+          <t>anamavi79@gmail.com</t>
         </is>
       </c>
       <c r="U18" t="inlineStr">
         <is>
-          <t>PILAR</t>
+          <t>ANA</t>
         </is>
       </c>
       <c r="V18" t="inlineStr">
         <is>
-          <t>Perez</t>
+          <t>Díaz MORALES</t>
         </is>
       </c>
       <c r="W18" t="inlineStr"/>
@@ -4048,152 +4048,144 @@
       <c r="AF21" s="18" t="inlineStr"/>
     </row>
     <row r="22">
-      <c r="A22" t="inlineStr">
-        <is>
-          <t>Skimbit LTD</t>
-        </is>
-      </c>
-      <c r="B22" s="16" t="n">
-        <v>102</v>
-      </c>
-      <c r="C22" s="16" t="n">
-        <v>6.12</v>
-      </c>
-      <c r="D22" s="16" t="n">
-        <v>1.84</v>
-      </c>
-      <c r="E22" t="inlineStr">
-        <is>
-          <t>10/23/25 22:24</t>
-        </is>
-      </c>
-      <c r="F22" t="inlineStr">
-        <is>
-          <t>81350</t>
-        </is>
-      </c>
-      <c r="G22" t="inlineStr">
-        <is>
-          <t>ES</t>
-        </is>
-      </c>
-      <c r="H22" t="inlineStr">
+      <c r="A22" s="21" t="inlineStr">
+        <is>
+          <t>Digital Expand</t>
+        </is>
+      </c>
+      <c r="B22" s="22" t="n">
+        <v>84.5</v>
+      </c>
+      <c r="C22" s="22" t="n">
+        <v>5.07</v>
+      </c>
+      <c r="D22" s="22" t="n">
+        <v>1.52</v>
+      </c>
+      <c r="E22" s="21" t="inlineStr">
+        <is>
+          <t>10/22/25 18:06</t>
+        </is>
+      </c>
+      <c r="F22" s="21" t="inlineStr">
+        <is>
+          <t>81238</t>
+        </is>
+      </c>
+      <c r="G22" s="21" t="inlineStr">
+        <is>
+          <t>ES</t>
+        </is>
+      </c>
+      <c r="H22" s="21" t="inlineStr">
         <is>
           <t>Reventa</t>
         </is>
       </c>
-      <c r="I22" s="17" t="inlineStr">
+      <c r="I22" s="23" t="inlineStr">
         <is>
           <t>6%</t>
         </is>
       </c>
-      <c r="J22" t="inlineStr">
-        <is>
-          <t>Adidas Samba OG Core Black</t>
-        </is>
-      </c>
-      <c r="K22" t="inlineStr">
-        <is>
-          <t>44 EU - 10 US</t>
-        </is>
-      </c>
-      <c r="L22" t="inlineStr">
-        <is>
-          <t>B75807</t>
-        </is>
-      </c>
-      <c r="M22" t="inlineStr">
-        <is>
-          <t>PAID</t>
-        </is>
-      </c>
-      <c r="N22" t="inlineStr">
+      <c r="J22" s="21" t="inlineStr">
+        <is>
+          <t>Puma Speedcat Zebra</t>
+        </is>
+      </c>
+      <c r="K22" s="21" t="inlineStr">
+        <is>
+          <t>40.5 EU - 8 US</t>
+        </is>
+      </c>
+      <c r="L22" s="21" t="inlineStr">
+        <is>
+          <t>403356-01</t>
+        </is>
+      </c>
+      <c r="M22" s="21" t="inlineStr">
+        <is>
+          <t>REFUNDED</t>
+        </is>
+      </c>
+      <c r="N22" s="21" t="inlineStr">
         <is>
           <t>FULFILLED</t>
         </is>
       </c>
-      <c r="O22" t="inlineStr">
+      <c r="O22" s="21" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="P22" t="inlineStr"/>
-      <c r="Q22" t="inlineStr"/>
-      <c r="R22" t="inlineStr"/>
-      <c r="S22" t="inlineStr"/>
-      <c r="T22" t="inlineStr">
-        <is>
-          <t>iserranomartinez98@gmail.com</t>
-        </is>
-      </c>
-      <c r="U22" t="inlineStr">
-        <is>
-          <t>Isaac</t>
-        </is>
-      </c>
-      <c r="V22" t="inlineStr">
-        <is>
-          <t>Serrano Martinez</t>
-        </is>
-      </c>
-      <c r="W22" t="inlineStr"/>
-      <c r="X22" t="inlineStr">
-        <is>
-          <t>Repeat Customer (Order #2)</t>
-        </is>
-      </c>
-      <c r="Y22" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="Z22" t="inlineStr">
-        <is>
-          <t>Google</t>
-        </is>
-      </c>
-      <c r="AA22" t="inlineStr">
-        <is>
-          <t>google</t>
-        </is>
-      </c>
-      <c r="AB22" t="inlineStr">
-        <is>
-          <t>cpc</t>
-        </is>
-      </c>
-      <c r="AC22" t="inlineStr">
-        <is>
-          <t>{campaignname}</t>
-        </is>
-      </c>
-      <c r="AD22" t="inlineStr"/>
-      <c r="AE22" t="inlineStr"/>
-      <c r="AF22" t="inlineStr"/>
+      <c r="P22" s="21" t="inlineStr">
+        <is>
+          <t>REFUNDED</t>
+        </is>
+      </c>
+      <c r="Q22" s="21" t="inlineStr"/>
+      <c r="R22" s="21" t="inlineStr"/>
+      <c r="S22" s="21" t="inlineStr">
+        <is>
+          <t>PEDIDO CANCELADO</t>
+        </is>
+      </c>
+      <c r="T22" s="21" t="inlineStr">
+        <is>
+          <t>lauramallo@hotmail.es</t>
+        </is>
+      </c>
+      <c r="U22" s="21" t="inlineStr">
+        <is>
+          <t>Laura</t>
+        </is>
+      </c>
+      <c r="V22" s="21" t="inlineStr">
+        <is>
+          <t>Mallo De Prado</t>
+        </is>
+      </c>
+      <c r="W22" s="21" t="inlineStr"/>
+      <c r="X22" s="21" t="inlineStr">
+        <is>
+          <t>First Order</t>
+        </is>
+      </c>
+      <c r="Y22" s="21" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="Z22" s="21" t="inlineStr"/>
+      <c r="AA22" s="21" t="inlineStr"/>
+      <c r="AB22" s="21" t="inlineStr"/>
+      <c r="AC22" s="21" t="inlineStr"/>
+      <c r="AD22" s="21" t="inlineStr"/>
+      <c r="AE22" s="21" t="inlineStr"/>
+      <c r="AF22" s="21" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" s="18" t="inlineStr">
         <is>
-          <t>Digital Expand</t>
+          <t>BlueVision Interactive Limited</t>
         </is>
       </c>
       <c r="B23" s="19" t="n">
-        <v>110</v>
+        <v>314.9</v>
       </c>
       <c r="C23" s="19" t="n">
-        <v>5.5</v>
+        <v>15.75</v>
       </c>
       <c r="D23" s="19" t="n">
-        <v>1.65</v>
+        <v>4.72</v>
       </c>
       <c r="E23" s="18" t="inlineStr">
         <is>
-          <t>10/22/25 18:00</t>
+          <t>10/22/25 10:59</t>
         </is>
       </c>
       <c r="F23" s="18" t="inlineStr">
         <is>
-          <t>81235</t>
+          <t>81182</t>
         </is>
       </c>
       <c r="G23" s="18" t="inlineStr">
@@ -4213,17 +4205,17 @@
       </c>
       <c r="J23" s="18" t="inlineStr">
         <is>
-          <t>Puma LaMelo Ball LaFrancé Amour Moment</t>
+          <t>Air Jordan 11 Retro Cherry (2022), Black Cargo Trousers</t>
         </is>
       </c>
       <c r="K23" s="18" t="inlineStr">
         <is>
-          <t>47 EU - 13 US</t>
+          <t>38 EU - 5.5 US, S</t>
         </is>
       </c>
       <c r="L23" s="18" t="inlineStr">
         <is>
-          <t>310864-01</t>
+          <t>378038-116, IKAO2</t>
         </is>
       </c>
       <c r="M23" s="18" t="inlineStr">
@@ -4247,28 +4239,28 @@
       <c r="S23" s="18" t="inlineStr"/>
       <c r="T23" s="18" t="inlineStr">
         <is>
-          <t>CANMARI_83@HOTMAIL.COM</t>
+          <t>dleon3750@gmail.com</t>
         </is>
       </c>
       <c r="U23" s="18" t="inlineStr">
         <is>
-          <t>Carmen María</t>
+          <t>Daniel Sebastian</t>
         </is>
       </c>
       <c r="V23" s="18" t="inlineStr">
         <is>
-          <t>González Solís</t>
+          <t>Torres Leon</t>
         </is>
       </c>
       <c r="W23" s="18" t="inlineStr"/>
       <c r="X23" s="18" t="inlineStr">
         <is>
-          <t>First Order</t>
+          <t>Repeat Customer (Order #3)</t>
         </is>
       </c>
       <c r="Y23" s="18" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>3</t>
         </is>
       </c>
       <c r="Z23" s="18" t="inlineStr">
@@ -4284,144 +4276,152 @@
       <c r="AF23" s="18" t="inlineStr"/>
     </row>
     <row r="24">
-      <c r="A24" s="21" t="inlineStr">
-        <is>
-          <t>Digital Expand</t>
-        </is>
-      </c>
-      <c r="B24" s="22" t="n">
-        <v>84.5</v>
-      </c>
-      <c r="C24" s="22" t="n">
-        <v>5.07</v>
-      </c>
-      <c r="D24" s="22" t="n">
-        <v>1.52</v>
-      </c>
-      <c r="E24" s="21" t="inlineStr">
-        <is>
-          <t>10/22/25 18:06</t>
-        </is>
-      </c>
-      <c r="F24" s="21" t="inlineStr">
-        <is>
-          <t>81238</t>
-        </is>
-      </c>
-      <c r="G24" s="21" t="inlineStr">
-        <is>
-          <t>ES</t>
-        </is>
-      </c>
-      <c r="H24" s="21" t="inlineStr">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>Skimbit LTD</t>
+        </is>
+      </c>
+      <c r="B24" s="16" t="n">
+        <v>102</v>
+      </c>
+      <c r="C24" s="16" t="n">
+        <v>6.12</v>
+      </c>
+      <c r="D24" s="16" t="n">
+        <v>1.84</v>
+      </c>
+      <c r="E24" t="inlineStr">
+        <is>
+          <t>10/23/25 22:24</t>
+        </is>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>81350</t>
+        </is>
+      </c>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>ES</t>
+        </is>
+      </c>
+      <c r="H24" t="inlineStr">
         <is>
           <t>Reventa</t>
         </is>
       </c>
-      <c r="I24" s="23" t="inlineStr">
+      <c r="I24" s="17" t="inlineStr">
         <is>
           <t>6%</t>
         </is>
       </c>
-      <c r="J24" s="21" t="inlineStr">
-        <is>
-          <t>Puma Speedcat Zebra</t>
-        </is>
-      </c>
-      <c r="K24" s="21" t="inlineStr">
-        <is>
-          <t>40.5 EU - 8 US</t>
-        </is>
-      </c>
-      <c r="L24" s="21" t="inlineStr">
-        <is>
-          <t>403356-01</t>
-        </is>
-      </c>
-      <c r="M24" s="21" t="inlineStr">
-        <is>
-          <t>REFUNDED</t>
-        </is>
-      </c>
-      <c r="N24" s="21" t="inlineStr">
+      <c r="J24" t="inlineStr">
+        <is>
+          <t>Adidas Samba OG Core Black</t>
+        </is>
+      </c>
+      <c r="K24" t="inlineStr">
+        <is>
+          <t>44 EU - 10 US</t>
+        </is>
+      </c>
+      <c r="L24" t="inlineStr">
+        <is>
+          <t>B75807</t>
+        </is>
+      </c>
+      <c r="M24" t="inlineStr">
+        <is>
+          <t>PAID</t>
+        </is>
+      </c>
+      <c r="N24" t="inlineStr">
         <is>
           <t>FULFILLED</t>
         </is>
       </c>
-      <c r="O24" s="21" t="inlineStr">
+      <c r="O24" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="P24" s="21" t="inlineStr">
-        <is>
-          <t>REFUNDED</t>
-        </is>
-      </c>
-      <c r="Q24" s="21" t="inlineStr"/>
-      <c r="R24" s="21" t="inlineStr"/>
-      <c r="S24" s="21" t="inlineStr">
-        <is>
-          <t>PEDIDO CANCELADO</t>
-        </is>
-      </c>
-      <c r="T24" s="21" t="inlineStr">
-        <is>
-          <t>lauramallo@hotmail.es</t>
-        </is>
-      </c>
-      <c r="U24" s="21" t="inlineStr">
-        <is>
-          <t>Laura</t>
-        </is>
-      </c>
-      <c r="V24" s="21" t="inlineStr">
-        <is>
-          <t>Mallo De Prado</t>
-        </is>
-      </c>
-      <c r="W24" s="21" t="inlineStr"/>
-      <c r="X24" s="21" t="inlineStr">
-        <is>
-          <t>First Order</t>
-        </is>
-      </c>
-      <c r="Y24" s="21" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="Z24" s="21" t="inlineStr"/>
-      <c r="AA24" s="21" t="inlineStr"/>
-      <c r="AB24" s="21" t="inlineStr"/>
-      <c r="AC24" s="21" t="inlineStr"/>
-      <c r="AD24" s="21" t="inlineStr"/>
-      <c r="AE24" s="21" t="inlineStr"/>
-      <c r="AF24" s="21" t="inlineStr"/>
+      <c r="P24" t="inlineStr"/>
+      <c r="Q24" t="inlineStr"/>
+      <c r="R24" t="inlineStr"/>
+      <c r="S24" t="inlineStr"/>
+      <c r="T24" t="inlineStr">
+        <is>
+          <t>iserranomartinez98@gmail.com</t>
+        </is>
+      </c>
+      <c r="U24" t="inlineStr">
+        <is>
+          <t>Isaac</t>
+        </is>
+      </c>
+      <c r="V24" t="inlineStr">
+        <is>
+          <t>Serrano Martinez</t>
+        </is>
+      </c>
+      <c r="W24" t="inlineStr"/>
+      <c r="X24" t="inlineStr">
+        <is>
+          <t>Repeat Customer (Order #2)</t>
+        </is>
+      </c>
+      <c r="Y24" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="Z24" t="inlineStr">
+        <is>
+          <t>Google</t>
+        </is>
+      </c>
+      <c r="AA24" t="inlineStr">
+        <is>
+          <t>google</t>
+        </is>
+      </c>
+      <c r="AB24" t="inlineStr">
+        <is>
+          <t>cpc</t>
+        </is>
+      </c>
+      <c r="AC24" t="inlineStr">
+        <is>
+          <t>{campaignname}</t>
+        </is>
+      </c>
+      <c r="AD24" t="inlineStr"/>
+      <c r="AE24" t="inlineStr"/>
+      <c r="AF24" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" s="18" t="inlineStr">
         <is>
-          <t>BlueVision Interactive Limited</t>
+          <t>Digital Expand</t>
         </is>
       </c>
       <c r="B25" s="19" t="n">
-        <v>314.9</v>
+        <v>110</v>
       </c>
       <c r="C25" s="19" t="n">
-        <v>15.75</v>
+        <v>5.5</v>
       </c>
       <c r="D25" s="19" t="n">
-        <v>4.72</v>
+        <v>1.65</v>
       </c>
       <c r="E25" s="18" t="inlineStr">
         <is>
-          <t>10/22/25 10:59</t>
+          <t>10/22/25 18:00</t>
         </is>
       </c>
       <c r="F25" s="18" t="inlineStr">
         <is>
-          <t>81182</t>
+          <t>81235</t>
         </is>
       </c>
       <c r="G25" s="18" t="inlineStr">
@@ -4441,17 +4441,17 @@
       </c>
       <c r="J25" s="18" t="inlineStr">
         <is>
-          <t>Air Jordan 11 Retro Cherry (2022), Black Cargo Trousers</t>
+          <t>Puma LaMelo Ball LaFrancé Amour Moment</t>
         </is>
       </c>
       <c r="K25" s="18" t="inlineStr">
         <is>
-          <t>38 EU - 5.5 US, S</t>
+          <t>47 EU - 13 US</t>
         </is>
       </c>
       <c r="L25" s="18" t="inlineStr">
         <is>
-          <t>378038-116, IKAO2</t>
+          <t>310864-01</t>
         </is>
       </c>
       <c r="M25" s="18" t="inlineStr">
@@ -4475,28 +4475,28 @@
       <c r="S25" s="18" t="inlineStr"/>
       <c r="T25" s="18" t="inlineStr">
         <is>
-          <t>dleon3750@gmail.com</t>
+          <t>CANMARI_83@HOTMAIL.COM</t>
         </is>
       </c>
       <c r="U25" s="18" t="inlineStr">
         <is>
-          <t>Daniel Sebastian</t>
+          <t>Carmen María</t>
         </is>
       </c>
       <c r="V25" s="18" t="inlineStr">
         <is>
-          <t>Torres Leon</t>
+          <t>González Solís</t>
         </is>
       </c>
       <c r="W25" s="18" t="inlineStr"/>
       <c r="X25" s="18" t="inlineStr">
         <is>
-          <t>Repeat Customer (Order #3)</t>
+          <t>First Order</t>
         </is>
       </c>
       <c r="Y25" s="18" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>1</t>
         </is>
       </c>
       <c r="Z25" s="18" t="inlineStr">
@@ -4514,31 +4514,31 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Deal Savings LLC</t>
+          <t>Skimbit LTD</t>
         </is>
       </c>
       <c r="B26" s="16" t="n">
-        <v>102</v>
+        <v>150</v>
       </c>
       <c r="C26" s="16" t="n">
-        <v>6.12</v>
+        <v>9</v>
       </c>
       <c r="D26" s="16" t="n">
-        <v>1.84</v>
+        <v>2.7</v>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>10/20/25 10:11</t>
+          <t>10/21/25 23:07</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>81037</t>
+          <t>81173</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>ES</t>
+          <t>FR</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
@@ -4553,17 +4553,17 @@
       </c>
       <c r="J26" t="inlineStr">
         <is>
-          <t>Adidas Samba OG Core Black</t>
+          <t>Fear of God Essentials Hoodie Fleece Black</t>
         </is>
       </c>
       <c r="K26" t="inlineStr">
         <is>
-          <t>39.3 EU - 6.5 US</t>
+          <t>XS</t>
         </is>
       </c>
       <c r="L26" t="inlineStr">
         <is>
-          <t>B75807</t>
+          <t>192HO246250F</t>
         </is>
       </c>
       <c r="M26" t="inlineStr">
@@ -4587,17 +4587,17 @@
       <c r="S26" t="inlineStr"/>
       <c r="T26" t="inlineStr">
         <is>
-          <t>jbo@ekonomistak.eus</t>
+          <t>SERGE19860629@HOTMAIL.COM</t>
         </is>
       </c>
       <c r="U26" t="inlineStr">
         <is>
-          <t>JAVIER</t>
+          <t>kai</t>
         </is>
       </c>
       <c r="V26" t="inlineStr">
         <is>
-          <t>BORDONABE ODRIOZOLA</t>
+          <t>yu</t>
         </is>
       </c>
       <c r="W26" t="inlineStr"/>
@@ -4626,31 +4626,31 @@
     <row r="27">
       <c r="A27" s="18" t="inlineStr">
         <is>
-          <t>Skimbit LTD</t>
+          <t>Deal Savings LLC</t>
         </is>
       </c>
       <c r="B27" s="19" t="n">
-        <v>150</v>
+        <v>102</v>
       </c>
       <c r="C27" s="19" t="n">
-        <v>9</v>
+        <v>6.12</v>
       </c>
       <c r="D27" s="19" t="n">
-        <v>2.7</v>
+        <v>1.84</v>
       </c>
       <c r="E27" s="18" t="inlineStr">
         <is>
-          <t>10/21/25 23:07</t>
+          <t>10/20/25 10:11</t>
         </is>
       </c>
       <c r="F27" s="18" t="inlineStr">
         <is>
-          <t>81173</t>
+          <t>81037</t>
         </is>
       </c>
       <c r="G27" s="18" t="inlineStr">
         <is>
-          <t>FR</t>
+          <t>ES</t>
         </is>
       </c>
       <c r="H27" s="18" t="inlineStr">
@@ -4665,17 +4665,17 @@
       </c>
       <c r="J27" s="18" t="inlineStr">
         <is>
-          <t>Fear of God Essentials Hoodie Fleece Black</t>
+          <t>Adidas Samba OG Core Black</t>
         </is>
       </c>
       <c r="K27" s="18" t="inlineStr">
         <is>
-          <t>XS</t>
+          <t>39.3 EU - 6.5 US</t>
         </is>
       </c>
       <c r="L27" s="18" t="inlineStr">
         <is>
-          <t>192HO246250F</t>
+          <t>B75807</t>
         </is>
       </c>
       <c r="M27" s="18" t="inlineStr">
@@ -4699,17 +4699,17 @@
       <c r="S27" s="18" t="inlineStr"/>
       <c r="T27" s="18" t="inlineStr">
         <is>
-          <t>SERGE19860629@HOTMAIL.COM</t>
+          <t>jbo@ekonomistak.eus</t>
         </is>
       </c>
       <c r="U27" s="18" t="inlineStr">
         <is>
-          <t>kai</t>
+          <t>JAVIER</t>
         </is>
       </c>
       <c r="V27" s="18" t="inlineStr">
         <is>
-          <t>yu</t>
+          <t>BORDONABE ODRIOZOLA</t>
         </is>
       </c>
       <c r="W27" s="18" t="inlineStr"/>
@@ -4738,26 +4738,26 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Shoparize</t>
+          <t>Invoke AB</t>
         </is>
       </c>
       <c r="B28" s="16" t="n">
-        <v>100</v>
+        <v>96</v>
       </c>
       <c r="C28" s="16" t="n">
-        <v>5</v>
+        <v>4.8</v>
       </c>
       <c r="D28" s="16" t="n">
-        <v>1.5</v>
+        <v>1.44</v>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>10/19/25 21:03</t>
+          <t>10/19/25 18:19</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>81033</t>
+          <t>81015</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
@@ -4777,17 +4777,17 @@
       </c>
       <c r="J28" t="inlineStr">
         <is>
-          <t>Adidas Handball Spezial Earth Strata Gum</t>
+          <t>Adidas Samba OG Earth Strata Wonder White</t>
         </is>
       </c>
       <c r="K28" t="inlineStr">
         <is>
-          <t>37.3 EU - 5 US</t>
+          <t>39.3 EU - 6.5 US</t>
         </is>
       </c>
       <c r="L28" t="inlineStr">
         <is>
-          <t>IF6490</t>
+          <t>JI3184</t>
         </is>
       </c>
       <c r="M28" t="inlineStr">
@@ -4811,17 +4811,17 @@
       <c r="S28" t="inlineStr"/>
       <c r="T28" t="inlineStr">
         <is>
-          <t>shaki_8@yahoo.es</t>
+          <t>juridico2@equityasesores.es</t>
         </is>
       </c>
       <c r="U28" t="inlineStr">
         <is>
-          <t>Maria</t>
+          <t>Elena</t>
         </is>
       </c>
       <c r="V28" t="inlineStr">
         <is>
-          <t>Perez Moreno</t>
+          <t>Chornet Pons</t>
         </is>
       </c>
       <c r="W28" t="inlineStr"/>
@@ -4860,272 +4860,272 @@
       <c r="AF28" t="inlineStr"/>
     </row>
     <row r="29">
-      <c r="A29" s="18" t="inlineStr">
-        <is>
-          <t>Invoke AB</t>
-        </is>
-      </c>
-      <c r="B29" s="19" t="n">
-        <v>96</v>
-      </c>
-      <c r="C29" s="19" t="n">
-        <v>4.8</v>
-      </c>
-      <c r="D29" s="19" t="n">
-        <v>1.44</v>
-      </c>
-      <c r="E29" s="18" t="inlineStr">
-        <is>
-          <t>10/19/25 18:19</t>
-        </is>
-      </c>
-      <c r="F29" s="18" t="inlineStr">
-        <is>
-          <t>81015</t>
-        </is>
-      </c>
-      <c r="G29" s="18" t="inlineStr">
-        <is>
-          <t>ES</t>
-        </is>
-      </c>
-      <c r="H29" s="18" t="inlineStr">
+      <c r="A29" s="24" t="inlineStr">
+        <is>
+          <t>LINKGAINS PTE.LTD.</t>
+        </is>
+      </c>
+      <c r="B29" s="25" t="n">
+        <v>185</v>
+      </c>
+      <c r="C29" s="25" t="n">
+        <v>9.6</v>
+      </c>
+      <c r="D29" s="25" t="n">
+        <v>2.88</v>
+      </c>
+      <c r="E29" s="24" t="inlineStr">
+        <is>
+          <t>10/19/25 09:51</t>
+        </is>
+      </c>
+      <c r="F29" s="24" t="inlineStr">
+        <is>
+          <t>80931</t>
+        </is>
+      </c>
+      <c r="G29" s="24" t="inlineStr">
+        <is>
+          <t>FR</t>
+        </is>
+      </c>
+      <c r="H29" s="24" t="inlineStr">
         <is>
           <t>Retail</t>
         </is>
       </c>
-      <c r="I29" s="20" t="inlineStr">
+      <c r="I29" s="26" t="inlineStr">
         <is>
           <t>5%</t>
         </is>
       </c>
-      <c r="J29" s="18" t="inlineStr">
-        <is>
-          <t>Adidas Samba OG Earth Strata Wonder White</t>
-        </is>
-      </c>
-      <c r="K29" s="18" t="inlineStr">
-        <is>
-          <t>39.3 EU - 6.5 US</t>
-        </is>
-      </c>
-      <c r="L29" s="18" t="inlineStr">
-        <is>
-          <t>JI3184</t>
-        </is>
-      </c>
-      <c r="M29" s="18" t="inlineStr">
+      <c r="J29" s="24" t="inlineStr">
+        <is>
+          <t>Dunk Low Light Armory Blue Photon Dust From, Crep Protect Cure Travel Kit, Crep Protect Spray 200 ml</t>
+        </is>
+      </c>
+      <c r="K29" s="24" t="inlineStr">
+        <is>
+          <t>44 EU - 10 US, UNICO, UNICO</t>
+        </is>
+      </c>
+      <c r="L29" s="24" t="inlineStr">
+        <is>
+          <t>FZ3779-025, 8820-285, 8807-277</t>
+        </is>
+      </c>
+      <c r="M29" s="24" t="inlineStr">
+        <is>
+          <t>REFUNDED</t>
+        </is>
+      </c>
+      <c r="N29" s="24" t="inlineStr">
+        <is>
+          <t>UNFULFILLED</t>
+        </is>
+      </c>
+      <c r="O29" s="24" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="P29" s="24" t="inlineStr">
+        <is>
+          <t>CANCELLED | REFUNDED</t>
+        </is>
+      </c>
+      <c r="Q29" s="24" t="inlineStr"/>
+      <c r="R29" s="24" t="inlineStr"/>
+      <c r="S29" s="24" t="inlineStr">
+        <is>
+          <t>PEDIDO CANCELADO</t>
+        </is>
+      </c>
+      <c r="T29" s="24" t="inlineStr">
+        <is>
+          <t>eliott.trivel@gmail.com</t>
+        </is>
+      </c>
+      <c r="U29" s="24" t="inlineStr">
+        <is>
+          <t>Eliott</t>
+        </is>
+      </c>
+      <c r="V29" s="24" t="inlineStr">
+        <is>
+          <t>Trivel</t>
+        </is>
+      </c>
+      <c r="W29" s="24" t="inlineStr"/>
+      <c r="X29" s="24" t="inlineStr">
+        <is>
+          <t>First Order</t>
+        </is>
+      </c>
+      <c r="Y29" s="24" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="Z29" s="24" t="inlineStr">
+        <is>
+          <t>Google</t>
+        </is>
+      </c>
+      <c r="AA29" s="24" t="inlineStr"/>
+      <c r="AB29" s="24" t="inlineStr"/>
+      <c r="AC29" s="24" t="inlineStr"/>
+      <c r="AD29" s="24" t="inlineStr"/>
+      <c r="AE29" s="24" t="inlineStr"/>
+      <c r="AF29" s="24" t="inlineStr"/>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>Shoparize</t>
+        </is>
+      </c>
+      <c r="B30" s="16" t="n">
+        <v>100</v>
+      </c>
+      <c r="C30" s="16" t="n">
+        <v>5</v>
+      </c>
+      <c r="D30" s="16" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="E30" t="inlineStr">
+        <is>
+          <t>10/19/25 21:03</t>
+        </is>
+      </c>
+      <c r="F30" t="inlineStr">
+        <is>
+          <t>81033</t>
+        </is>
+      </c>
+      <c r="G30" t="inlineStr">
+        <is>
+          <t>ES</t>
+        </is>
+      </c>
+      <c r="H30" t="inlineStr">
+        <is>
+          <t>Retail</t>
+        </is>
+      </c>
+      <c r="I30" s="17" t="inlineStr">
+        <is>
+          <t>5%</t>
+        </is>
+      </c>
+      <c r="J30" t="inlineStr">
+        <is>
+          <t>Adidas Handball Spezial Earth Strata Gum</t>
+        </is>
+      </c>
+      <c r="K30" t="inlineStr">
+        <is>
+          <t>37.3 EU - 5 US</t>
+        </is>
+      </c>
+      <c r="L30" t="inlineStr">
+        <is>
+          <t>IF6490</t>
+        </is>
+      </c>
+      <c r="M30" t="inlineStr">
         <is>
           <t>PAID</t>
         </is>
       </c>
-      <c r="N29" s="18" t="inlineStr">
+      <c r="N30" t="inlineStr">
         <is>
           <t>FULFILLED</t>
         </is>
       </c>
-      <c r="O29" s="18" t="inlineStr">
+      <c r="O30" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="P29" s="18" t="inlineStr"/>
-      <c r="Q29" s="18" t="inlineStr"/>
-      <c r="R29" s="18" t="inlineStr"/>
-      <c r="S29" s="18" t="inlineStr"/>
-      <c r="T29" s="18" t="inlineStr">
-        <is>
-          <t>juridico2@equityasesores.es</t>
-        </is>
-      </c>
-      <c r="U29" s="18" t="inlineStr">
-        <is>
-          <t>Elena</t>
-        </is>
-      </c>
-      <c r="V29" s="18" t="inlineStr">
-        <is>
-          <t>Chornet Pons</t>
-        </is>
-      </c>
-      <c r="W29" s="18" t="inlineStr"/>
-      <c r="X29" s="18" t="inlineStr">
+      <c r="P30" t="inlineStr"/>
+      <c r="Q30" t="inlineStr"/>
+      <c r="R30" t="inlineStr"/>
+      <c r="S30" t="inlineStr"/>
+      <c r="T30" t="inlineStr">
+        <is>
+          <t>shaki_8@yahoo.es</t>
+        </is>
+      </c>
+      <c r="U30" t="inlineStr">
+        <is>
+          <t>Maria</t>
+        </is>
+      </c>
+      <c r="V30" t="inlineStr">
+        <is>
+          <t>Perez Moreno</t>
+        </is>
+      </c>
+      <c r="W30" t="inlineStr"/>
+      <c r="X30" t="inlineStr">
         <is>
           <t>First Order</t>
         </is>
       </c>
-      <c r="Y29" s="18" t="inlineStr">
+      <c r="Y30" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="Z29" s="18" t="inlineStr">
+      <c r="Z30" t="inlineStr">
         <is>
           <t>Google</t>
         </is>
       </c>
-      <c r="AA29" s="18" t="inlineStr">
+      <c r="AA30" t="inlineStr">
         <is>
           <t>google</t>
         </is>
       </c>
-      <c r="AB29" s="18" t="inlineStr">
+      <c r="AB30" t="inlineStr">
         <is>
           <t>cpc</t>
         </is>
       </c>
-      <c r="AC29" s="18" t="inlineStr">
+      <c r="AC30" t="inlineStr">
         <is>
           <t>{campaignname}</t>
         </is>
       </c>
-      <c r="AD29" s="18" t="inlineStr"/>
-      <c r="AE29" s="18" t="inlineStr"/>
-      <c r="AF29" s="18" t="inlineStr"/>
-    </row>
-    <row r="30">
-      <c r="A30" s="24" t="inlineStr">
-        <is>
-          <t>LINKGAINS PTE.LTD.</t>
-        </is>
-      </c>
-      <c r="B30" s="25" t="n">
-        <v>185</v>
-      </c>
-      <c r="C30" s="25" t="n">
-        <v>9.6</v>
-      </c>
-      <c r="D30" s="25" t="n">
-        <v>2.88</v>
-      </c>
-      <c r="E30" s="24" t="inlineStr">
-        <is>
-          <t>10/19/25 09:51</t>
-        </is>
-      </c>
-      <c r="F30" s="24" t="inlineStr">
-        <is>
-          <t>80931</t>
-        </is>
-      </c>
-      <c r="G30" s="24" t="inlineStr">
-        <is>
-          <t>FR</t>
-        </is>
-      </c>
-      <c r="H30" s="24" t="inlineStr">
-        <is>
-          <t>Retail</t>
-        </is>
-      </c>
-      <c r="I30" s="26" t="inlineStr">
-        <is>
-          <t>5%</t>
-        </is>
-      </c>
-      <c r="J30" s="24" t="inlineStr">
-        <is>
-          <t>Dunk Low Light Armory Blue Photon Dust From, Crep Protect Cure Travel Kit, Crep Protect Spray 200 ml</t>
-        </is>
-      </c>
-      <c r="K30" s="24" t="inlineStr">
-        <is>
-          <t>44 EU - 10 US, UNICO, UNICO</t>
-        </is>
-      </c>
-      <c r="L30" s="24" t="inlineStr">
-        <is>
-          <t>FZ3779-025, 8820-285, 8807-277</t>
-        </is>
-      </c>
-      <c r="M30" s="24" t="inlineStr">
-        <is>
-          <t>REFUNDED</t>
-        </is>
-      </c>
-      <c r="N30" s="24" t="inlineStr">
-        <is>
-          <t>UNFULFILLED</t>
-        </is>
-      </c>
-      <c r="O30" s="24" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="P30" s="24" t="inlineStr">
-        <is>
-          <t>CANCELLED | REFUNDED</t>
-        </is>
-      </c>
-      <c r="Q30" s="24" t="inlineStr"/>
-      <c r="R30" s="24" t="inlineStr"/>
-      <c r="S30" s="24" t="inlineStr">
-        <is>
-          <t>PEDIDO CANCELADO</t>
-        </is>
-      </c>
-      <c r="T30" s="24" t="inlineStr">
-        <is>
-          <t>eliott.trivel@gmail.com</t>
-        </is>
-      </c>
-      <c r="U30" s="24" t="inlineStr">
-        <is>
-          <t>Eliott</t>
-        </is>
-      </c>
-      <c r="V30" s="24" t="inlineStr">
-        <is>
-          <t>Trivel</t>
-        </is>
-      </c>
-      <c r="W30" s="24" t="inlineStr"/>
-      <c r="X30" s="24" t="inlineStr">
-        <is>
-          <t>First Order</t>
-        </is>
-      </c>
-      <c r="Y30" s="24" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="Z30" s="24" t="inlineStr">
-        <is>
-          <t>Google</t>
-        </is>
-      </c>
-      <c r="AA30" s="24" t="inlineStr"/>
-      <c r="AB30" s="24" t="inlineStr"/>
-      <c r="AC30" s="24" t="inlineStr"/>
-      <c r="AD30" s="24" t="inlineStr"/>
-      <c r="AE30" s="24" t="inlineStr"/>
-      <c r="AF30" s="24" t="inlineStr"/>
+      <c r="AD30" t="inlineStr"/>
+      <c r="AE30" t="inlineStr"/>
+      <c r="AF30" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" s="18" t="inlineStr">
         <is>
-          <t>LINKGAINS PTE.LTD.</t>
+          <t>BlueVision Interactive Limited</t>
         </is>
       </c>
       <c r="B31" s="19" t="n">
-        <v>89</v>
+        <v>99</v>
       </c>
       <c r="C31" s="19" t="n">
-        <v>5.34</v>
+        <v>5.94</v>
       </c>
       <c r="D31" s="19" t="n">
-        <v>1.6</v>
+        <v>1.78</v>
       </c>
       <c r="E31" s="18" t="inlineStr">
         <is>
-          <t>10/18/25 16:27</t>
+          <t>10/19/25 00:09</t>
         </is>
       </c>
       <c r="F31" s="18" t="inlineStr">
         <is>
-          <t>80872</t>
+          <t>80926</t>
         </is>
       </c>
       <c r="G31" s="18" t="inlineStr">
@@ -5145,17 +5145,17 @@
       </c>
       <c r="J31" s="18" t="inlineStr">
         <is>
-          <t>Adidas Handball Spezial Dark Brown Wonder Mauve</t>
+          <t>Adidas SL 72 RS Earth Strata Warm Vanilla</t>
         </is>
       </c>
       <c r="K31" s="18" t="inlineStr">
         <is>
-          <t>37.3 EU - 5 US</t>
+          <t>38 EU - 5.5 US</t>
         </is>
       </c>
       <c r="L31" s="18" t="inlineStr">
         <is>
-          <t>JR0852</t>
+          <t>JR8774</t>
         </is>
       </c>
       <c r="M31" s="18" t="inlineStr">
@@ -5175,42 +5175,58 @@
       </c>
       <c r="P31" s="18" t="inlineStr"/>
       <c r="Q31" s="18" t="inlineStr"/>
-      <c r="R31" s="18" t="inlineStr"/>
+      <c r="R31" s="18" t="inlineStr">
+        <is>
+          <t>RETURN IN PROCESS</t>
+        </is>
+      </c>
       <c r="S31" s="18" t="inlineStr"/>
       <c r="T31" s="18" t="inlineStr">
         <is>
-          <t>veronicasosacastellano@gmail.com</t>
+          <t>angy.kabaeva@gmail.com</t>
         </is>
       </c>
       <c r="U31" s="18" t="inlineStr">
         <is>
-          <t>Veronica</t>
+          <t>Angela</t>
         </is>
       </c>
       <c r="V31" s="18" t="inlineStr">
         <is>
-          <t>Sosa</t>
+          <t>Lopez Cuevas</t>
         </is>
       </c>
       <c r="W31" s="18" t="inlineStr"/>
       <c r="X31" s="18" t="inlineStr">
         <is>
-          <t>First Order</t>
+          <t>Repeat Customer (Order #2)</t>
         </is>
       </c>
       <c r="Y31" s="18" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="Z31" s="18" t="inlineStr">
         <is>
-          <t>direct</t>
-        </is>
-      </c>
-      <c r="AA31" s="18" t="inlineStr"/>
-      <c r="AB31" s="18" t="inlineStr"/>
-      <c r="AC31" s="18" t="inlineStr"/>
+          <t>an unknown source</t>
+        </is>
+      </c>
+      <c r="AA31" s="18" t="inlineStr">
+        <is>
+          <t>google</t>
+        </is>
+      </c>
+      <c r="AB31" s="18" t="inlineStr">
+        <is>
+          <t>cpc</t>
+        </is>
+      </c>
+      <c r="AC31" s="18" t="inlineStr">
+        <is>
+          <t>{campaignname}</t>
+        </is>
+      </c>
       <c r="AD31" s="18" t="inlineStr"/>
       <c r="AE31" s="18" t="inlineStr"/>
       <c r="AF31" s="18" t="inlineStr"/>
@@ -5218,26 +5234,26 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>BlueVision Interactive Limited</t>
+          <t>LINKGAINS PTE.LTD.</t>
         </is>
       </c>
       <c r="B32" s="16" t="n">
-        <v>99</v>
+        <v>89</v>
       </c>
       <c r="C32" s="16" t="n">
-        <v>5.94</v>
+        <v>5.34</v>
       </c>
       <c r="D32" s="16" t="n">
-        <v>1.78</v>
+        <v>1.6</v>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>10/19/25 00:09</t>
+          <t>10/18/25 16:27</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>80926</t>
+          <t>80872</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
@@ -5257,17 +5273,17 @@
       </c>
       <c r="J32" t="inlineStr">
         <is>
-          <t>Adidas SL 72 RS Earth Strata Warm Vanilla</t>
+          <t>Adidas Handball Spezial Dark Brown Wonder Mauve</t>
         </is>
       </c>
       <c r="K32" t="inlineStr">
         <is>
-          <t>38 EU - 5.5 US</t>
+          <t>37.3 EU - 5 US</t>
         </is>
       </c>
       <c r="L32" t="inlineStr">
         <is>
-          <t>JR8774</t>
+          <t>JR0852</t>
         </is>
       </c>
       <c r="M32" t="inlineStr">
@@ -5287,58 +5303,42 @@
       </c>
       <c r="P32" t="inlineStr"/>
       <c r="Q32" t="inlineStr"/>
-      <c r="R32" t="inlineStr">
-        <is>
-          <t>RETURN IN PROCESS</t>
-        </is>
-      </c>
+      <c r="R32" t="inlineStr"/>
       <c r="S32" t="inlineStr"/>
       <c r="T32" t="inlineStr">
         <is>
-          <t>angy.kabaeva@gmail.com</t>
+          <t>veronicasosacastellano@gmail.com</t>
         </is>
       </c>
       <c r="U32" t="inlineStr">
         <is>
-          <t>Angela</t>
+          <t>Veronica</t>
         </is>
       </c>
       <c r="V32" t="inlineStr">
         <is>
-          <t>Lopez Cuevas</t>
+          <t>Sosa</t>
         </is>
       </c>
       <c r="W32" t="inlineStr"/>
       <c r="X32" t="inlineStr">
         <is>
-          <t>Repeat Customer (Order #2)</t>
+          <t>First Order</t>
         </is>
       </c>
       <c r="Y32" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="Z32" t="inlineStr">
         <is>
-          <t>an unknown source</t>
-        </is>
-      </c>
-      <c r="AA32" t="inlineStr">
-        <is>
-          <t>google</t>
-        </is>
-      </c>
-      <c r="AB32" t="inlineStr">
-        <is>
-          <t>cpc</t>
-        </is>
-      </c>
-      <c r="AC32" t="inlineStr">
-        <is>
-          <t>{campaignname}</t>
-        </is>
-      </c>
+          <t>direct</t>
+        </is>
+      </c>
+      <c r="AA32" t="inlineStr"/>
+      <c r="AB32" t="inlineStr"/>
+      <c r="AC32" t="inlineStr"/>
       <c r="AD32" t="inlineStr"/>
       <c r="AE32" t="inlineStr"/>
       <c r="AF32" t="inlineStr"/>
@@ -5572,380 +5572,380 @@
       <c r="AF34" t="inlineStr"/>
     </row>
     <row r="35">
-      <c r="A35" s="18" t="inlineStr">
+      <c r="A35" s="21" t="inlineStr">
+        <is>
+          <t>BlueVision Interactive Limited</t>
+        </is>
+      </c>
+      <c r="B35" s="22" t="n">
+        <v>79</v>
+      </c>
+      <c r="C35" s="22" t="n">
+        <v>3.95</v>
+      </c>
+      <c r="D35" s="22" t="n">
+        <v>1.19</v>
+      </c>
+      <c r="E35" s="21" t="inlineStr">
+        <is>
+          <t>10/14/25 21:47</t>
+        </is>
+      </c>
+      <c r="F35" s="21" t="inlineStr">
+        <is>
+          <t>80603</t>
+        </is>
+      </c>
+      <c r="G35" s="21" t="inlineStr">
+        <is>
+          <t>ES</t>
+        </is>
+      </c>
+      <c r="H35" s="21" t="inlineStr">
+        <is>
+          <t>Retail</t>
+        </is>
+      </c>
+      <c r="I35" s="23" t="inlineStr">
+        <is>
+          <t>5%</t>
+        </is>
+      </c>
+      <c r="J35" s="21" t="inlineStr">
+        <is>
+          <t>Fakegods Valentines Hoodie Dark Grey</t>
+        </is>
+      </c>
+      <c r="K35" s="21" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="L35" s="21" t="inlineStr">
+        <is>
+          <t>VHDG</t>
+        </is>
+      </c>
+      <c r="M35" s="21" t="inlineStr">
+        <is>
+          <t>PARTIALLY_REFUNDED</t>
+        </is>
+      </c>
+      <c r="N35" s="21" t="inlineStr">
+        <is>
+          <t>FULFILLED</t>
+        </is>
+      </c>
+      <c r="O35" s="21" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="P35" s="21" t="inlineStr">
+        <is>
+          <t>PARTIALLY_REFUNDED</t>
+        </is>
+      </c>
+      <c r="Q35" s="21" t="inlineStr">
+        <is>
+          <t>79.00 EUR / 79.00 EUR</t>
+        </is>
+      </c>
+      <c r="R35" s="21" t="inlineStr"/>
+      <c r="S35" s="21" t="inlineStr">
+        <is>
+          <t>Issue (PARTIALLY REFUNDED)</t>
+        </is>
+      </c>
+      <c r="T35" s="21" t="inlineStr">
+        <is>
+          <t>evalabradormartinez@hotmail.com</t>
+        </is>
+      </c>
+      <c r="U35" s="21" t="inlineStr">
+        <is>
+          <t>Eva</t>
+        </is>
+      </c>
+      <c r="V35" s="21" t="inlineStr">
+        <is>
+          <t>Labrador Martinez</t>
+        </is>
+      </c>
+      <c r="W35" s="21" t="inlineStr"/>
+      <c r="X35" s="21" t="inlineStr">
+        <is>
+          <t>First Order</t>
+        </is>
+      </c>
+      <c r="Y35" s="21" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="Z35" s="21" t="inlineStr">
+        <is>
+          <t>direct</t>
+        </is>
+      </c>
+      <c r="AA35" s="21" t="inlineStr"/>
+      <c r="AB35" s="21" t="inlineStr"/>
+      <c r="AC35" s="21" t="inlineStr"/>
+      <c r="AD35" s="21" t="inlineStr"/>
+      <c r="AE35" s="21" t="inlineStr"/>
+      <c r="AF35" s="21" t="inlineStr"/>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
         <is>
           <t>Skimbit LTD</t>
         </is>
       </c>
-      <c r="B35" s="19" t="n">
+      <c r="B36" s="16" t="n">
         <v>120</v>
       </c>
-      <c r="C35" s="19" t="n">
+      <c r="C36" s="16" t="n">
         <v>7.2</v>
       </c>
-      <c r="D35" s="19" t="n">
+      <c r="D36" s="16" t="n">
         <v>2.16</v>
       </c>
-      <c r="E35" s="18" t="inlineStr">
+      <c r="E36" t="inlineStr">
         <is>
           <t>10/14/25 16:56</t>
         </is>
       </c>
-      <c r="F35" s="18" t="inlineStr">
+      <c r="F36" t="inlineStr">
         <is>
           <t>80572</t>
         </is>
       </c>
-      <c r="G35" s="18" t="inlineStr">
-        <is>
-          <t>ES</t>
-        </is>
-      </c>
-      <c r="H35" s="18" t="inlineStr">
+      <c r="G36" t="inlineStr">
+        <is>
+          <t>ES</t>
+        </is>
+      </c>
+      <c r="H36" t="inlineStr">
         <is>
           <t>Reventa</t>
         </is>
       </c>
-      <c r="I35" s="20" t="inlineStr">
+      <c r="I36" s="17" t="inlineStr">
         <is>
           <t>6%</t>
         </is>
       </c>
-      <c r="J35" s="18" t="inlineStr">
+      <c r="J36" t="inlineStr">
         <is>
           <t>Puma LaMelo Ball LaFrancé 3x Black</t>
         </is>
       </c>
-      <c r="K35" s="18" t="inlineStr">
+      <c r="K36" t="inlineStr">
         <is>
           <t>41 EU - 8.5 US</t>
         </is>
       </c>
-      <c r="L35" s="18" t="inlineStr">
+      <c r="L36" t="inlineStr">
         <is>
           <t>313081-01</t>
         </is>
       </c>
-      <c r="M35" s="18" t="inlineStr">
+      <c r="M36" t="inlineStr">
         <is>
           <t>PAID</t>
         </is>
       </c>
-      <c r="N35" s="18" t="inlineStr">
+      <c r="N36" t="inlineStr">
         <is>
           <t>FULFILLED</t>
         </is>
       </c>
-      <c r="O35" s="18" t="inlineStr">
+      <c r="O36" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="P35" s="18" t="inlineStr"/>
-      <c r="Q35" s="18" t="inlineStr"/>
-      <c r="R35" s="18" t="inlineStr"/>
-      <c r="S35" s="18" t="inlineStr"/>
-      <c r="T35" s="18" t="inlineStr">
+      <c r="P36" t="inlineStr"/>
+      <c r="Q36" t="inlineStr"/>
+      <c r="R36" t="inlineStr"/>
+      <c r="S36" t="inlineStr"/>
+      <c r="T36" t="inlineStr">
         <is>
           <t>patrickhuamani05@gmail.com</t>
         </is>
       </c>
-      <c r="U35" s="18" t="inlineStr">
+      <c r="U36" t="inlineStr">
         <is>
           <t>Patrick</t>
         </is>
       </c>
-      <c r="V35" s="18" t="inlineStr">
+      <c r="V36" t="inlineStr">
         <is>
           <t>Huamani Najarro</t>
         </is>
       </c>
-      <c r="W35" s="18" t="inlineStr"/>
-      <c r="X35" s="18" t="inlineStr">
+      <c r="W36" t="inlineStr"/>
+      <c r="X36" t="inlineStr">
         <is>
           <t>First Order</t>
         </is>
       </c>
-      <c r="Y35" s="18" t="inlineStr">
+      <c r="Y36" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="Z35" s="18" t="inlineStr">
+      <c r="Z36" t="inlineStr">
         <is>
           <t>Google</t>
         </is>
       </c>
-      <c r="AA35" s="18" t="inlineStr">
+      <c r="AA36" t="inlineStr">
         <is>
           <t>google</t>
         </is>
       </c>
-      <c r="AB35" s="18" t="inlineStr">
+      <c r="AB36" t="inlineStr">
         <is>
           <t>cpc</t>
         </is>
       </c>
-      <c r="AC35" s="18" t="inlineStr">
+      <c r="AC36" t="inlineStr">
         <is>
           <t>{campaignname}</t>
         </is>
       </c>
-      <c r="AD35" s="18" t="inlineStr"/>
-      <c r="AE35" s="18" t="inlineStr"/>
-      <c r="AF35" s="18" t="inlineStr"/>
-    </row>
-    <row r="36">
-      <c r="A36" s="24" t="inlineStr">
+      <c r="AD36" t="inlineStr"/>
+      <c r="AE36" t="inlineStr"/>
+      <c r="AF36" t="inlineStr"/>
+    </row>
+    <row r="37">
+      <c r="A37" s="24" t="inlineStr">
         <is>
           <t>Skimbit LTD</t>
         </is>
       </c>
-      <c r="B36" s="25" t="n">
+      <c r="B37" s="25" t="n">
         <v>102</v>
       </c>
-      <c r="C36" s="25" t="n">
+      <c r="C37" s="25" t="n">
         <v>6.12</v>
       </c>
-      <c r="D36" s="25" t="n">
+      <c r="D37" s="25" t="n">
         <v>1.84</v>
       </c>
-      <c r="E36" s="24" t="inlineStr">
+      <c r="E37" s="24" t="inlineStr">
         <is>
           <t>10/14/25 18:53</t>
         </is>
       </c>
-      <c r="F36" s="24" t="inlineStr">
+      <c r="F37" s="24" t="inlineStr">
         <is>
           <t>80587</t>
         </is>
       </c>
-      <c r="G36" s="24" t="inlineStr">
-        <is>
-          <t>ES</t>
-        </is>
-      </c>
-      <c r="H36" s="24" t="inlineStr">
+      <c r="G37" s="24" t="inlineStr">
+        <is>
+          <t>ES</t>
+        </is>
+      </c>
+      <c r="H37" s="24" t="inlineStr">
         <is>
           <t>Reventa</t>
         </is>
       </c>
-      <c r="I36" s="26" t="inlineStr">
+      <c r="I37" s="26" t="inlineStr">
         <is>
           <t>6%</t>
         </is>
       </c>
-      <c r="J36" s="24" t="inlineStr">
+      <c r="J37" s="24" t="inlineStr">
         <is>
           <t>Adidas Samba OG Cloud White</t>
         </is>
       </c>
-      <c r="K36" s="24" t="inlineStr">
+      <c r="K37" s="24" t="inlineStr">
         <is>
           <t>40.6 EU - 7.5 US</t>
         </is>
       </c>
-      <c r="L36" s="24" t="inlineStr">
+      <c r="L37" s="24" t="inlineStr">
         <is>
           <t>B75806</t>
         </is>
       </c>
-      <c r="M36" s="24" t="inlineStr">
+      <c r="M37" s="24" t="inlineStr">
         <is>
           <t>EXPIRED</t>
         </is>
       </c>
-      <c r="N36" s="24" t="inlineStr">
+      <c r="N37" s="24" t="inlineStr">
         <is>
           <t>UNFULFILLED</t>
         </is>
       </c>
-      <c r="O36" s="24" t="inlineStr">
+      <c r="O37" s="24" t="inlineStr">
         <is>
           <t>Yes</t>
         </is>
       </c>
-      <c r="P36" s="24" t="inlineStr">
+      <c r="P37" s="24" t="inlineStr">
         <is>
           <t>CANCELLED</t>
         </is>
       </c>
-      <c r="Q36" s="24" t="inlineStr"/>
-      <c r="R36" s="24" t="inlineStr"/>
-      <c r="S36" s="24" t="inlineStr">
+      <c r="Q37" s="24" t="inlineStr"/>
+      <c r="R37" s="24" t="inlineStr"/>
+      <c r="S37" s="24" t="inlineStr">
         <is>
           <t>PEDIDO NO PREPARADO</t>
         </is>
       </c>
-      <c r="T36" s="24" t="inlineStr">
+      <c r="T37" s="24" t="inlineStr">
         <is>
           <t>serafinatellez04@gmail.com</t>
         </is>
       </c>
-      <c r="U36" s="24" t="inlineStr">
+      <c r="U37" s="24" t="inlineStr">
         <is>
           <t>Karla</t>
         </is>
       </c>
-      <c r="V36" s="24" t="inlineStr">
+      <c r="V37" s="24" t="inlineStr">
         <is>
           <t>Ruiz</t>
         </is>
       </c>
-      <c r="W36" s="24" t="inlineStr">
+      <c r="W37" s="24" t="inlineStr">
         <is>
           <t>+34613368017</t>
         </is>
       </c>
-      <c r="X36" s="24" t="inlineStr">
+      <c r="X37" s="24" t="inlineStr">
         <is>
           <t>First Order</t>
         </is>
       </c>
-      <c r="Y36" s="24" t="inlineStr">
+      <c r="Y37" s="24" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="Z36" s="24" t="inlineStr">
+      <c r="Z37" s="24" t="inlineStr">
         <is>
           <t>https://www.sequra.com/</t>
         </is>
       </c>
-      <c r="AA36" s="24" t="inlineStr">
+      <c r="AA37" s="24" t="inlineStr">
         <is>
           <t>webgains</t>
         </is>
       </c>
-      <c r="AB36" s="24" t="inlineStr"/>
-      <c r="AC36" s="24" t="inlineStr"/>
-      <c r="AD36" s="24" t="inlineStr"/>
-      <c r="AE36" s="24" t="inlineStr"/>
-      <c r="AF36" s="24" t="inlineStr"/>
-    </row>
-    <row r="37">
-      <c r="A37" s="21" t="inlineStr">
-        <is>
-          <t>BlueVision Interactive Limited</t>
-        </is>
-      </c>
-      <c r="B37" s="22" t="n">
-        <v>79</v>
-      </c>
-      <c r="C37" s="22" t="n">
-        <v>3.95</v>
-      </c>
-      <c r="D37" s="22" t="n">
-        <v>1.19</v>
-      </c>
-      <c r="E37" s="21" t="inlineStr">
-        <is>
-          <t>10/14/25 21:47</t>
-        </is>
-      </c>
-      <c r="F37" s="21" t="inlineStr">
-        <is>
-          <t>80603</t>
-        </is>
-      </c>
-      <c r="G37" s="21" t="inlineStr">
-        <is>
-          <t>ES</t>
-        </is>
-      </c>
-      <c r="H37" s="21" t="inlineStr">
-        <is>
-          <t>Retail</t>
-        </is>
-      </c>
-      <c r="I37" s="23" t="inlineStr">
-        <is>
-          <t>5%</t>
-        </is>
-      </c>
-      <c r="J37" s="21" t="inlineStr">
-        <is>
-          <t>Fakegods Valentines Hoodie Dark Grey</t>
-        </is>
-      </c>
-      <c r="K37" s="21" t="inlineStr">
-        <is>
-          <t>M</t>
-        </is>
-      </c>
-      <c r="L37" s="21" t="inlineStr">
-        <is>
-          <t>VHDG</t>
-        </is>
-      </c>
-      <c r="M37" s="21" t="inlineStr">
-        <is>
-          <t>PARTIALLY_REFUNDED</t>
-        </is>
-      </c>
-      <c r="N37" s="21" t="inlineStr">
-        <is>
-          <t>FULFILLED</t>
-        </is>
-      </c>
-      <c r="O37" s="21" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="P37" s="21" t="inlineStr">
-        <is>
-          <t>PARTIALLY_REFUNDED</t>
-        </is>
-      </c>
-      <c r="Q37" s="21" t="inlineStr">
-        <is>
-          <t>79.00 EUR / 79.00 EUR</t>
-        </is>
-      </c>
-      <c r="R37" s="21" t="inlineStr"/>
-      <c r="S37" s="21" t="inlineStr">
-        <is>
-          <t>Issue (PARTIALLY REFUNDED)</t>
-        </is>
-      </c>
-      <c r="T37" s="21" t="inlineStr">
-        <is>
-          <t>evalabradormartinez@hotmail.com</t>
-        </is>
-      </c>
-      <c r="U37" s="21" t="inlineStr">
-        <is>
-          <t>Eva</t>
-        </is>
-      </c>
-      <c r="V37" s="21" t="inlineStr">
-        <is>
-          <t>Labrador Martinez</t>
-        </is>
-      </c>
-      <c r="W37" s="21" t="inlineStr"/>
-      <c r="X37" s="21" t="inlineStr">
-        <is>
-          <t>First Order</t>
-        </is>
-      </c>
-      <c r="Y37" s="21" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="Z37" s="21" t="inlineStr">
-        <is>
-          <t>direct</t>
-        </is>
-      </c>
-      <c r="AA37" s="21" t="inlineStr"/>
-      <c r="AB37" s="21" t="inlineStr"/>
-      <c r="AC37" s="21" t="inlineStr"/>
-      <c r="AD37" s="21" t="inlineStr"/>
-      <c r="AE37" s="21" t="inlineStr"/>
-      <c r="AF37" s="21" t="inlineStr"/>
+      <c r="AB37" s="24" t="inlineStr"/>
+      <c r="AC37" s="24" t="inlineStr"/>
+      <c r="AD37" s="24" t="inlineStr"/>
+      <c r="AE37" s="24" t="inlineStr"/>
+      <c r="AF37" s="24" t="inlineStr"/>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
@@ -6043,12 +6043,12 @@
       </c>
       <c r="X38" t="inlineStr">
         <is>
-          <t>Repeat Customer (Order #12)</t>
+          <t>Repeat Customer (Order #13)</t>
         </is>
       </c>
       <c r="Y38" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>13</t>
         </is>
       </c>
       <c r="Z38" t="inlineStr">
@@ -6418,26 +6418,26 @@
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>AFILIZA</t>
+          <t>Skimbit LTD</t>
         </is>
       </c>
       <c r="B42" s="16" t="n">
-        <v>96</v>
+        <v>270</v>
       </c>
       <c r="C42" s="16" t="n">
-        <v>4.8</v>
+        <v>13.5</v>
       </c>
       <c r="D42" s="16" t="n">
-        <v>1.44</v>
+        <v>4.05</v>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>10/12/25 14:51</t>
+          <t>10/12/25 13:04</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>80384</t>
+          <t>80372</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
@@ -6457,17 +6457,17 @@
       </c>
       <c r="J42" t="inlineStr">
         <is>
-          <t>Adidas Samba OG Earth Strata Wonder White</t>
+          <t>New Balance 530 White Silver Navy, Nike Air Force 1 Low 07 Triple White</t>
         </is>
       </c>
       <c r="K42" t="inlineStr">
         <is>
-          <t>39.3 EU - 6.5 US</t>
+          <t>40 EU - 7 US, 40 EU - 7 US</t>
         </is>
       </c>
       <c r="L42" t="inlineStr">
         <is>
-          <t>JI3184</t>
+          <t>MR530SG, CW2288-111</t>
         </is>
       </c>
       <c r="M42" t="inlineStr">
@@ -6491,50 +6491,46 @@
       <c r="S42" t="inlineStr"/>
       <c r="T42" t="inlineStr">
         <is>
-          <t>vesteve1987@hotmail.com</t>
+          <t>mariacasasauroglas@gmail.com</t>
         </is>
       </c>
       <c r="U42" t="inlineStr">
         <is>
-          <t>Victor</t>
+          <t>Maria Carolina</t>
         </is>
       </c>
       <c r="V42" t="inlineStr">
         <is>
-          <t>Esteve Agelet</t>
-        </is>
-      </c>
-      <c r="W42" t="inlineStr"/>
+          <t>Casas López</t>
+        </is>
+      </c>
+      <c r="W42" t="inlineStr">
+        <is>
+          <t>+34613275416</t>
+        </is>
+      </c>
       <c r="X42" t="inlineStr">
         <is>
-          <t>First Order</t>
+          <t>Repeat Customer (Order #2)</t>
         </is>
       </c>
       <c r="Y42" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="Z42" t="inlineStr">
         <is>
-          <t>Google</t>
+          <t>https://www.sequra.com/</t>
         </is>
       </c>
       <c r="AA42" t="inlineStr">
         <is>
-          <t>google</t>
-        </is>
-      </c>
-      <c r="AB42" t="inlineStr">
-        <is>
-          <t>cpc</t>
-        </is>
-      </c>
-      <c r="AC42" t="inlineStr">
-        <is>
-          <t>{campaignname}</t>
-        </is>
-      </c>
+          <t>webgains</t>
+        </is>
+      </c>
+      <c r="AB42" t="inlineStr"/>
+      <c r="AC42" t="inlineStr"/>
       <c r="AD42" t="inlineStr"/>
       <c r="AE42" t="inlineStr"/>
       <c r="AF42" t="inlineStr"/>
@@ -6542,26 +6538,26 @@
     <row r="43">
       <c r="A43" s="18" t="inlineStr">
         <is>
-          <t>Skimbit LTD</t>
+          <t>AFILIZA</t>
         </is>
       </c>
       <c r="B43" s="19" t="n">
-        <v>270</v>
+        <v>96</v>
       </c>
       <c r="C43" s="19" t="n">
-        <v>13.5</v>
+        <v>4.8</v>
       </c>
       <c r="D43" s="19" t="n">
-        <v>4.05</v>
+        <v>1.44</v>
       </c>
       <c r="E43" s="18" t="inlineStr">
         <is>
-          <t>10/12/25 13:04</t>
+          <t>10/12/25 14:51</t>
         </is>
       </c>
       <c r="F43" s="18" t="inlineStr">
         <is>
-          <t>80372</t>
+          <t>80384</t>
         </is>
       </c>
       <c r="G43" s="18" t="inlineStr">
@@ -6581,17 +6577,17 @@
       </c>
       <c r="J43" s="18" t="inlineStr">
         <is>
-          <t>New Balance 530 White Silver Navy, Nike Air Force 1 Low 07 Triple White</t>
+          <t>Adidas Samba OG Earth Strata Wonder White</t>
         </is>
       </c>
       <c r="K43" s="18" t="inlineStr">
         <is>
-          <t>40 EU - 7 US, 40 EU - 7 US</t>
+          <t>39.3 EU - 6.5 US</t>
         </is>
       </c>
       <c r="L43" s="18" t="inlineStr">
         <is>
-          <t>MR530SG, CW2288-111</t>
+          <t>JI3184</t>
         </is>
       </c>
       <c r="M43" s="18" t="inlineStr">
@@ -6615,46 +6611,50 @@
       <c r="S43" s="18" t="inlineStr"/>
       <c r="T43" s="18" t="inlineStr">
         <is>
-          <t>mariacasasauroglas@gmail.com</t>
+          <t>vesteve1987@hotmail.com</t>
         </is>
       </c>
       <c r="U43" s="18" t="inlineStr">
         <is>
-          <t>Maria Carolina</t>
+          <t>Victor</t>
         </is>
       </c>
       <c r="V43" s="18" t="inlineStr">
         <is>
-          <t>Casas López</t>
-        </is>
-      </c>
-      <c r="W43" s="18" t="inlineStr">
-        <is>
-          <t>+34613275416</t>
-        </is>
-      </c>
+          <t>Esteve Agelet</t>
+        </is>
+      </c>
+      <c r="W43" s="18" t="inlineStr"/>
       <c r="X43" s="18" t="inlineStr">
         <is>
-          <t>Repeat Customer (Order #2)</t>
+          <t>First Order</t>
         </is>
       </c>
       <c r="Y43" s="18" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="Z43" s="18" t="inlineStr">
         <is>
-          <t>https://www.sequra.com/</t>
+          <t>Google</t>
         </is>
       </c>
       <c r="AA43" s="18" t="inlineStr">
         <is>
-          <t>webgains</t>
-        </is>
-      </c>
-      <c r="AB43" s="18" t="inlineStr"/>
-      <c r="AC43" s="18" t="inlineStr"/>
+          <t>google</t>
+        </is>
+      </c>
+      <c r="AB43" s="18" t="inlineStr">
+        <is>
+          <t>cpc</t>
+        </is>
+      </c>
+      <c r="AC43" s="18" t="inlineStr">
+        <is>
+          <t>{campaignname}</t>
+        </is>
+      </c>
       <c r="AD43" s="18" t="inlineStr"/>
       <c r="AE43" s="18" t="inlineStr"/>
       <c r="AF43" s="18" t="inlineStr"/>
@@ -6914,22 +6914,22 @@
         </is>
       </c>
       <c r="B46" s="16" t="n">
-        <v>130</v>
+        <v>110</v>
       </c>
       <c r="C46" s="16" t="n">
-        <v>6.5</v>
+        <v>5.5</v>
       </c>
       <c r="D46" s="16" t="n">
-        <v>1.95</v>
+        <v>1.65</v>
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>10/09/25 08:34</t>
+          <t>10/10/25 18:32</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>80075</t>
+          <t>80196</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
@@ -6949,17 +6949,17 @@
       </c>
       <c r="J46" t="inlineStr">
         <is>
-          <t>Nike Air Force 1 Low 07 Triple White</t>
+          <t>Dunk Low Next Nature White Mint</t>
         </is>
       </c>
       <c r="K46" t="inlineStr">
         <is>
-          <t>44 EU - 10 US</t>
+          <t>35.5 EU - 3.5 US</t>
         </is>
       </c>
       <c r="L46" t="inlineStr">
         <is>
-          <t>CW2288-111</t>
+          <t>DN1431-102</t>
         </is>
       </c>
       <c r="M46" t="inlineStr">
@@ -6983,20 +6983,24 @@
       <c r="S46" t="inlineStr"/>
       <c r="T46" t="inlineStr">
         <is>
-          <t>marinagarciablanes24@gmail.com</t>
+          <t>cearva20@hotmail.com</t>
         </is>
       </c>
       <c r="U46" t="inlineStr">
         <is>
-          <t>Marina</t>
+          <t>Celia</t>
         </is>
       </c>
       <c r="V46" t="inlineStr">
         <is>
-          <t>García Blanes</t>
-        </is>
-      </c>
-      <c r="W46" t="inlineStr"/>
+          <t>Arenas</t>
+        </is>
+      </c>
+      <c r="W46" t="inlineStr">
+        <is>
+          <t>+34633044751</t>
+        </is>
+      </c>
       <c r="X46" t="inlineStr">
         <is>
           <t>First Order</t>
@@ -7146,22 +7150,22 @@
         </is>
       </c>
       <c r="B48" s="16" t="n">
-        <v>110</v>
+        <v>130</v>
       </c>
       <c r="C48" s="16" t="n">
-        <v>5.5</v>
+        <v>6.5</v>
       </c>
       <c r="D48" s="16" t="n">
-        <v>1.65</v>
+        <v>1.95</v>
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>10/10/25 18:32</t>
+          <t>10/09/25 08:34</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>80196</t>
+          <t>80075</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
@@ -7181,17 +7185,17 @@
       </c>
       <c r="J48" t="inlineStr">
         <is>
-          <t>Dunk Low Next Nature White Mint</t>
+          <t>Nike Air Force 1 Low 07 Triple White</t>
         </is>
       </c>
       <c r="K48" t="inlineStr">
         <is>
-          <t>35.5 EU - 3.5 US</t>
+          <t>44 EU - 10 US</t>
         </is>
       </c>
       <c r="L48" t="inlineStr">
         <is>
-          <t>DN1431-102</t>
+          <t>CW2288-111</t>
         </is>
       </c>
       <c r="M48" t="inlineStr">
@@ -7215,24 +7219,20 @@
       <c r="S48" t="inlineStr"/>
       <c r="T48" t="inlineStr">
         <is>
-          <t>cearva20@hotmail.com</t>
+          <t>marinagarciablanes24@gmail.com</t>
         </is>
       </c>
       <c r="U48" t="inlineStr">
         <is>
-          <t>Celia</t>
+          <t>Marina</t>
         </is>
       </c>
       <c r="V48" t="inlineStr">
         <is>
-          <t>Arenas</t>
-        </is>
-      </c>
-      <c r="W48" t="inlineStr">
-        <is>
-          <t>+34633044751</t>
-        </is>
-      </c>
+          <t>García Blanes</t>
+        </is>
+      </c>
+      <c r="W48" t="inlineStr"/>
       <c r="X48" t="inlineStr">
         <is>
           <t>First Order</t>
@@ -7620,160 +7620,140 @@
       <c r="AF51" s="18" t="inlineStr"/>
     </row>
     <row r="52">
-      <c r="A52" s="21" t="inlineStr">
-        <is>
-          <t>Pashion.dk ApS</t>
-        </is>
-      </c>
-      <c r="B52" s="22" t="n">
-        <v>450</v>
-      </c>
-      <c r="C52" s="22" t="n">
-        <v>22.5</v>
-      </c>
-      <c r="D52" s="22" t="n">
-        <v>6.75</v>
-      </c>
-      <c r="E52" s="21" t="inlineStr">
-        <is>
-          <t>10/05/25 12:16</t>
-        </is>
-      </c>
-      <c r="F52" s="21" t="inlineStr">
-        <is>
-          <t>79766</t>
-        </is>
-      </c>
-      <c r="G52" s="21" t="inlineStr">
-        <is>
-          <t>ES</t>
-        </is>
-      </c>
-      <c r="H52" s="21" t="inlineStr">
-        <is>
-          <t>Retail</t>
-        </is>
-      </c>
-      <c r="I52" s="23" t="inlineStr">
-        <is>
-          <t>5%</t>
-        </is>
-      </c>
-      <c r="J52" s="21" t="inlineStr">
-        <is>
-          <t>Air Jordan 4 Retro White Thunder</t>
-        </is>
-      </c>
-      <c r="K52" s="21" t="inlineStr">
-        <is>
-          <t>40 EU - 7 US</t>
-        </is>
-      </c>
-      <c r="L52" s="21" t="inlineStr">
-        <is>
-          <t>FQ8213-001</t>
-        </is>
-      </c>
-      <c r="M52" s="21" t="inlineStr">
-        <is>
-          <t>REFUNDED</t>
-        </is>
-      </c>
-      <c r="N52" s="21" t="inlineStr">
+      <c r="A52" t="inlineStr">
+        <is>
+          <t>Skimbit LTD</t>
+        </is>
+      </c>
+      <c r="B52" s="16" t="n">
+        <v>250</v>
+      </c>
+      <c r="C52" s="16" t="n">
+        <v>15</v>
+      </c>
+      <c r="D52" s="16" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="E52" t="inlineStr">
+        <is>
+          <t>10/05/25 01:11</t>
+        </is>
+      </c>
+      <c r="F52" t="inlineStr">
+        <is>
+          <t>79760</t>
+        </is>
+      </c>
+      <c r="G52" t="inlineStr">
+        <is>
+          <t>ES</t>
+        </is>
+      </c>
+      <c r="H52" t="inlineStr">
+        <is>
+          <t>Reventa</t>
+        </is>
+      </c>
+      <c r="I52" s="17" t="inlineStr">
+        <is>
+          <t>6%</t>
+        </is>
+      </c>
+      <c r="J52" t="inlineStr">
+        <is>
+          <t>Air Jordan 4 Retro White Cement</t>
+        </is>
+      </c>
+      <c r="K52" t="inlineStr">
+        <is>
+          <t>39 EU - 6.5 US</t>
+        </is>
+      </c>
+      <c r="L52" t="inlineStr">
+        <is>
+          <t>FV5029-100</t>
+        </is>
+      </c>
+      <c r="M52" t="inlineStr">
+        <is>
+          <t>PAID</t>
+        </is>
+      </c>
+      <c r="N52" t="inlineStr">
         <is>
           <t>FULFILLED</t>
         </is>
       </c>
-      <c r="O52" s="21" t="inlineStr">
+      <c r="O52" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="P52" s="21" t="inlineStr">
-        <is>
-          <t>REFUNDED</t>
-        </is>
-      </c>
-      <c r="Q52" s="21" t="inlineStr"/>
-      <c r="R52" s="21" t="inlineStr"/>
-      <c r="S52" s="21" t="inlineStr">
-        <is>
-          <t>PEDIDO CANCELADO</t>
-        </is>
-      </c>
-      <c r="T52" s="21" t="inlineStr">
-        <is>
-          <t>soccusretro@gmail.com</t>
-        </is>
-      </c>
-      <c r="U52" s="21" t="inlineStr">
-        <is>
-          <t>Melbin</t>
-        </is>
-      </c>
-      <c r="V52" s="21" t="inlineStr">
-        <is>
-          <t>Segura</t>
-        </is>
-      </c>
-      <c r="W52" s="21" t="inlineStr"/>
-      <c r="X52" s="21" t="inlineStr">
+      <c r="P52" t="inlineStr"/>
+      <c r="Q52" t="inlineStr"/>
+      <c r="R52" t="inlineStr"/>
+      <c r="S52" t="inlineStr"/>
+      <c r="T52" t="inlineStr">
+        <is>
+          <t>brianstiven24@gmail.com</t>
+        </is>
+      </c>
+      <c r="U52" t="inlineStr">
+        <is>
+          <t>Angie marian</t>
+        </is>
+      </c>
+      <c r="V52" t="inlineStr">
+        <is>
+          <t>Arévalo muñoz</t>
+        </is>
+      </c>
+      <c r="W52" t="inlineStr"/>
+      <c r="X52" t="inlineStr">
         <is>
           <t>First Order</t>
         </is>
       </c>
-      <c r="Y52" s="21" t="inlineStr">
+      <c r="Y52" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="Z52" s="21" t="inlineStr">
-        <is>
-          <t>Google</t>
-        </is>
-      </c>
-      <c r="AA52" s="21" t="inlineStr">
-        <is>
-          <t>google</t>
-        </is>
-      </c>
-      <c r="AB52" s="21" t="inlineStr">
-        <is>
-          <t>cpc</t>
-        </is>
-      </c>
-      <c r="AC52" s="21" t="inlineStr">
-        <is>
-          <t>{campaignname}</t>
-        </is>
-      </c>
-      <c r="AD52" s="21" t="inlineStr"/>
-      <c r="AE52" s="21" t="inlineStr"/>
-      <c r="AF52" s="21" t="inlineStr"/>
+      <c r="Z52" t="inlineStr">
+        <is>
+          <t>https://www.sequra.com/</t>
+        </is>
+      </c>
+      <c r="AA52" t="inlineStr"/>
+      <c r="AB52" t="inlineStr"/>
+      <c r="AC52" t="inlineStr"/>
+      <c r="AD52" t="inlineStr"/>
+      <c r="AE52" t="inlineStr"/>
+      <c r="AF52" t="inlineStr"/>
     </row>
     <row r="53">
       <c r="A53" s="18" t="inlineStr">
         <is>
-          <t>Skimbit LTD</t>
+          <t>AFILIZA</t>
         </is>
       </c>
       <c r="B53" s="19" t="n">
-        <v>250</v>
+        <v>110</v>
       </c>
       <c r="C53" s="19" t="n">
-        <v>15</v>
+        <v>5.5</v>
       </c>
       <c r="D53" s="19" t="n">
-        <v>4.5</v>
+        <v>1.65</v>
       </c>
       <c r="E53" s="18" t="inlineStr">
         <is>
-          <t>10/05/25 01:11</t>
+          <t>10/04/25 19:13</t>
         </is>
       </c>
       <c r="F53" s="18" t="inlineStr">
         <is>
-          <t>79760</t>
+          <t>79730</t>
         </is>
       </c>
       <c r="G53" s="18" t="inlineStr">
@@ -7783,27 +7763,27 @@
       </c>
       <c r="H53" s="18" t="inlineStr">
         <is>
-          <t>Reventa</t>
+          <t>Retail</t>
         </is>
       </c>
       <c r="I53" s="20" t="inlineStr">
         <is>
-          <t>6%</t>
+          <t>5%</t>
         </is>
       </c>
       <c r="J53" s="18" t="inlineStr">
         <is>
-          <t>Air Jordan 4 Retro White Cement</t>
+          <t>Puma LaMelo Ball LaFrancé Amour Moment</t>
         </is>
       </c>
       <c r="K53" s="18" t="inlineStr">
         <is>
-          <t>39 EU - 6.5 US</t>
+          <t>41 EU - 8.5 US</t>
         </is>
       </c>
       <c r="L53" s="18" t="inlineStr">
         <is>
-          <t>FV5029-100</t>
+          <t>310864-01</t>
         </is>
       </c>
       <c r="M53" s="18" t="inlineStr">
@@ -7827,17 +7807,17 @@
       <c r="S53" s="18" t="inlineStr"/>
       <c r="T53" s="18" t="inlineStr">
         <is>
-          <t>brianstiven24@gmail.com</t>
+          <t>daniellisa.gomez23@gmail.com</t>
         </is>
       </c>
       <c r="U53" s="18" t="inlineStr">
         <is>
-          <t>Angie marian</t>
+          <t>daniel</t>
         </is>
       </c>
       <c r="V53" s="18" t="inlineStr">
         <is>
-          <t>Arévalo muñoz</t>
+          <t>lisa gomez</t>
         </is>
       </c>
       <c r="W53" s="18" t="inlineStr"/>
@@ -7853,163 +7833,183 @@
       </c>
       <c r="Z53" s="18" t="inlineStr">
         <is>
-          <t>https://www.sequra.com/</t>
-        </is>
-      </c>
-      <c r="AA53" s="18" t="inlineStr"/>
-      <c r="AB53" s="18" t="inlineStr"/>
-      <c r="AC53" s="18" t="inlineStr"/>
+          <t>Google</t>
+        </is>
+      </c>
+      <c r="AA53" s="18" t="inlineStr">
+        <is>
+          <t>google</t>
+        </is>
+      </c>
+      <c r="AB53" s="18" t="inlineStr">
+        <is>
+          <t>cpc</t>
+        </is>
+      </c>
+      <c r="AC53" s="18" t="inlineStr">
+        <is>
+          <t>{campaignname}</t>
+        </is>
+      </c>
       <c r="AD53" s="18" t="inlineStr"/>
       <c r="AE53" s="18" t="inlineStr"/>
       <c r="AF53" s="18" t="inlineStr"/>
     </row>
     <row r="54">
-      <c r="A54" t="inlineStr">
-        <is>
-          <t>Purplee Corp</t>
-        </is>
-      </c>
-      <c r="B54" s="16" t="n">
-        <v>89</v>
-      </c>
-      <c r="C54" s="16" t="n">
-        <v>5.34</v>
-      </c>
-      <c r="D54" s="16" t="n">
-        <v>1.6</v>
-      </c>
-      <c r="E54" t="inlineStr">
-        <is>
-          <t>10/04/25 17:01</t>
-        </is>
-      </c>
-      <c r="F54" t="inlineStr">
-        <is>
-          <t>79706</t>
-        </is>
-      </c>
-      <c r="G54" t="inlineStr">
-        <is>
-          <t>ES</t>
-        </is>
-      </c>
-      <c r="H54" t="inlineStr">
-        <is>
-          <t>Reventa</t>
-        </is>
-      </c>
-      <c r="I54" s="17" t="inlineStr">
-        <is>
-          <t>6%</t>
-        </is>
-      </c>
-      <c r="J54" t="inlineStr">
-        <is>
-          <t>Adidas Handball Spezial Navy Gum</t>
-        </is>
-      </c>
-      <c r="K54" t="inlineStr">
-        <is>
-          <t>40.6 EU - 7.5 US</t>
-        </is>
-      </c>
-      <c r="L54" t="inlineStr">
-        <is>
-          <t>BD7633</t>
-        </is>
-      </c>
-      <c r="M54" t="inlineStr">
-        <is>
-          <t>PAID</t>
-        </is>
-      </c>
-      <c r="N54" t="inlineStr">
+      <c r="A54" s="21" t="inlineStr">
+        <is>
+          <t>Pashion.dk ApS</t>
+        </is>
+      </c>
+      <c r="B54" s="22" t="n">
+        <v>450</v>
+      </c>
+      <c r="C54" s="22" t="n">
+        <v>22.5</v>
+      </c>
+      <c r="D54" s="22" t="n">
+        <v>6.75</v>
+      </c>
+      <c r="E54" s="21" t="inlineStr">
+        <is>
+          <t>10/05/25 12:16</t>
+        </is>
+      </c>
+      <c r="F54" s="21" t="inlineStr">
+        <is>
+          <t>79766</t>
+        </is>
+      </c>
+      <c r="G54" s="21" t="inlineStr">
+        <is>
+          <t>ES</t>
+        </is>
+      </c>
+      <c r="H54" s="21" t="inlineStr">
+        <is>
+          <t>Retail</t>
+        </is>
+      </c>
+      <c r="I54" s="23" t="inlineStr">
+        <is>
+          <t>5%</t>
+        </is>
+      </c>
+      <c r="J54" s="21" t="inlineStr">
+        <is>
+          <t>Air Jordan 4 Retro White Thunder</t>
+        </is>
+      </c>
+      <c r="K54" s="21" t="inlineStr">
+        <is>
+          <t>40 EU - 7 US</t>
+        </is>
+      </c>
+      <c r="L54" s="21" t="inlineStr">
+        <is>
+          <t>FQ8213-001</t>
+        </is>
+      </c>
+      <c r="M54" s="21" t="inlineStr">
+        <is>
+          <t>REFUNDED</t>
+        </is>
+      </c>
+      <c r="N54" s="21" t="inlineStr">
         <is>
           <t>FULFILLED</t>
         </is>
       </c>
-      <c r="O54" t="inlineStr">
+      <c r="O54" s="21" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="P54" t="inlineStr"/>
-      <c r="Q54" t="inlineStr"/>
-      <c r="R54" t="inlineStr"/>
-      <c r="S54" t="inlineStr"/>
-      <c r="T54" t="inlineStr">
-        <is>
-          <t>villamianacity@gmail.com</t>
-        </is>
-      </c>
-      <c r="U54" t="inlineStr">
-        <is>
-          <t>Clara</t>
-        </is>
-      </c>
-      <c r="V54" t="inlineStr">
-        <is>
-          <t>González Melgarejo</t>
-        </is>
-      </c>
-      <c r="W54" t="inlineStr"/>
-      <c r="X54" t="inlineStr">
+      <c r="P54" s="21" t="inlineStr">
+        <is>
+          <t>REFUNDED</t>
+        </is>
+      </c>
+      <c r="Q54" s="21" t="inlineStr"/>
+      <c r="R54" s="21" t="inlineStr"/>
+      <c r="S54" s="21" t="inlineStr">
+        <is>
+          <t>PEDIDO CANCELADO</t>
+        </is>
+      </c>
+      <c r="T54" s="21" t="inlineStr">
+        <is>
+          <t>soccusretro@gmail.com</t>
+        </is>
+      </c>
+      <c r="U54" s="21" t="inlineStr">
+        <is>
+          <t>Melbin</t>
+        </is>
+      </c>
+      <c r="V54" s="21" t="inlineStr">
+        <is>
+          <t>Segura</t>
+        </is>
+      </c>
+      <c r="W54" s="21" t="inlineStr"/>
+      <c r="X54" s="21" t="inlineStr">
         <is>
           <t>First Order</t>
         </is>
       </c>
-      <c r="Y54" t="inlineStr">
+      <c r="Y54" s="21" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="Z54" t="inlineStr">
+      <c r="Z54" s="21" t="inlineStr">
         <is>
           <t>Google</t>
         </is>
       </c>
-      <c r="AA54" t="inlineStr">
+      <c r="AA54" s="21" t="inlineStr">
         <is>
           <t>google</t>
         </is>
       </c>
-      <c r="AB54" t="inlineStr">
+      <c r="AB54" s="21" t="inlineStr">
         <is>
           <t>cpc</t>
         </is>
       </c>
-      <c r="AC54" t="inlineStr">
+      <c r="AC54" s="21" t="inlineStr">
         <is>
           <t>{campaignname}</t>
         </is>
       </c>
-      <c r="AD54" t="inlineStr"/>
-      <c r="AE54" t="inlineStr"/>
-      <c r="AF54" t="inlineStr"/>
+      <c r="AD54" s="21" t="inlineStr"/>
+      <c r="AE54" s="21" t="inlineStr"/>
+      <c r="AF54" s="21" t="inlineStr"/>
     </row>
     <row r="55">
       <c r="A55" s="18" t="inlineStr">
         <is>
-          <t>AFILIZA</t>
+          <t>Purplee Corp</t>
         </is>
       </c>
       <c r="B55" s="19" t="n">
-        <v>110</v>
+        <v>89</v>
       </c>
       <c r="C55" s="19" t="n">
-        <v>5.5</v>
+        <v>5.34</v>
       </c>
       <c r="D55" s="19" t="n">
-        <v>1.65</v>
+        <v>1.6</v>
       </c>
       <c r="E55" s="18" t="inlineStr">
         <is>
-          <t>10/04/25 19:13</t>
+          <t>10/04/25 17:01</t>
         </is>
       </c>
       <c r="F55" s="18" t="inlineStr">
         <is>
-          <t>79730</t>
+          <t>79706</t>
         </is>
       </c>
       <c r="G55" s="18" t="inlineStr">
@@ -8019,27 +8019,27 @@
       </c>
       <c r="H55" s="18" t="inlineStr">
         <is>
-          <t>Retail</t>
+          <t>Reventa</t>
         </is>
       </c>
       <c r="I55" s="20" t="inlineStr">
         <is>
-          <t>5%</t>
+          <t>6%</t>
         </is>
       </c>
       <c r="J55" s="18" t="inlineStr">
         <is>
-          <t>Puma LaMelo Ball LaFrancé Amour Moment</t>
+          <t>Adidas Handball Spezial Navy Gum</t>
         </is>
       </c>
       <c r="K55" s="18" t="inlineStr">
         <is>
-          <t>41 EU - 8.5 US</t>
+          <t>40.6 EU - 7.5 US</t>
         </is>
       </c>
       <c r="L55" s="18" t="inlineStr">
         <is>
-          <t>310864-01</t>
+          <t>BD7633</t>
         </is>
       </c>
       <c r="M55" s="18" t="inlineStr">
@@ -8063,17 +8063,17 @@
       <c r="S55" s="18" t="inlineStr"/>
       <c r="T55" s="18" t="inlineStr">
         <is>
-          <t>daniellisa.gomez23@gmail.com</t>
+          <t>villamianacity@gmail.com</t>
         </is>
       </c>
       <c r="U55" s="18" t="inlineStr">
         <is>
-          <t>daniel</t>
+          <t>Clara</t>
         </is>
       </c>
       <c r="V55" s="18" t="inlineStr">
         <is>
-          <t>lisa gomez</t>
+          <t>González Melgarejo</t>
         </is>
       </c>
       <c r="W55" s="18" t="inlineStr"/>
@@ -8230,26 +8230,26 @@
     <row r="57">
       <c r="A57" s="18" t="inlineStr">
         <is>
-          <t>Pashion.dk ApS</t>
+          <t>Skimbit LTD</t>
         </is>
       </c>
       <c r="B57" s="19" t="n">
-        <v>90</v>
+        <v>222</v>
       </c>
       <c r="C57" s="19" t="n">
-        <v>4.5</v>
+        <v>13.32</v>
       </c>
       <c r="D57" s="19" t="n">
-        <v>1.35</v>
+        <v>4</v>
       </c>
       <c r="E57" s="18" t="inlineStr">
         <is>
-          <t>10/04/25 12:10</t>
+          <t>10/03/25 11:13</t>
         </is>
       </c>
       <c r="F57" s="18" t="inlineStr">
         <is>
-          <t>79651</t>
+          <t>79575</t>
         </is>
       </c>
       <c r="G57" s="18" t="inlineStr">
@@ -8259,27 +8259,27 @@
       </c>
       <c r="H57" s="18" t="inlineStr">
         <is>
-          <t>Retail</t>
+          <t>Reventa</t>
         </is>
       </c>
       <c r="I57" s="20" t="inlineStr">
         <is>
-          <t>5%</t>
+          <t>6%</t>
         </is>
       </c>
       <c r="J57" s="18" t="inlineStr">
         <is>
-          <t>Dunk Low Court Purple (2022)</t>
+          <t>Adidas Campus 00s Camp Noble Maroon, Adidas Samba OG Fox Brown Off White Gum</t>
         </is>
       </c>
       <c r="K57" s="18" t="inlineStr">
         <is>
-          <t>45 EU - 11 US</t>
+          <t>39.3 EU - 6.5 US, 39.3 EU - 6.5 US</t>
         </is>
       </c>
       <c r="L57" s="18" t="inlineStr">
         <is>
-          <t>DD1391-104</t>
+          <t>JQ8349, JR0892</t>
         </is>
       </c>
       <c r="M57" s="18" t="inlineStr">
@@ -8303,17 +8303,17 @@
       <c r="S57" s="18" t="inlineStr"/>
       <c r="T57" s="18" t="inlineStr">
         <is>
-          <t>loukilichakri2008@gmail.com</t>
+          <t>dianapascual1984@gmail.com</t>
         </is>
       </c>
       <c r="U57" s="18" t="inlineStr">
         <is>
-          <t>Soufian</t>
+          <t>Diana</t>
         </is>
       </c>
       <c r="V57" s="18" t="inlineStr">
         <is>
-          <t>Chakri</t>
+          <t>Pascual Diaz</t>
         </is>
       </c>
       <c r="W57" s="18" t="inlineStr"/>
@@ -8329,7 +8329,7 @@
       </c>
       <c r="Z57" s="18" t="inlineStr">
         <is>
-          <t>Google</t>
+          <t>https://www.sequra.com/</t>
         </is>
       </c>
       <c r="AA57" s="18" t="inlineStr">
@@ -8346,26 +8346,26 @@
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>LINKGAINS PTE.LTD.</t>
+          <t>Pashion.dk ApS</t>
         </is>
       </c>
       <c r="B58" s="16" t="n">
-        <v>235</v>
+        <v>90</v>
       </c>
       <c r="C58" s="16" t="n">
-        <v>14.1</v>
+        <v>4.5</v>
       </c>
       <c r="D58" s="16" t="n">
-        <v>4.23</v>
+        <v>1.35</v>
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>10/02/25 15:28</t>
+          <t>10/04/25 12:10</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>79526</t>
+          <t>79651</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
@@ -8375,27 +8375,27 @@
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>Reventa</t>
+          <t>Retail</t>
         </is>
       </c>
       <c r="I58" s="17" t="inlineStr">
         <is>
-          <t>6%</t>
+          <t>5%</t>
         </is>
       </c>
       <c r="J58" t="inlineStr">
         <is>
-          <t>New Balance 204L Mushroom Arid Stone</t>
+          <t>Dunk Low Court Purple (2022)</t>
         </is>
       </c>
       <c r="K58" t="inlineStr">
         <is>
-          <t>38.5 EU - 6 US</t>
+          <t>45 EU - 11 US</t>
         </is>
       </c>
       <c r="L58" t="inlineStr">
         <is>
-          <t>U204LMMA</t>
+          <t>DD1391-104</t>
         </is>
       </c>
       <c r="M58" t="inlineStr">
@@ -8419,17 +8419,17 @@
       <c r="S58" t="inlineStr"/>
       <c r="T58" t="inlineStr">
         <is>
-          <t>lorealc1991@hotmail.com</t>
+          <t>loukilichakri2008@gmail.com</t>
         </is>
       </c>
       <c r="U58" t="inlineStr">
         <is>
-          <t>Lorena</t>
+          <t>Soufian</t>
         </is>
       </c>
       <c r="V58" t="inlineStr">
         <is>
-          <t>Cortes alcalde</t>
+          <t>Chakri</t>
         </is>
       </c>
       <c r="W58" t="inlineStr"/>
@@ -8448,7 +8448,11 @@
           <t>Google</t>
         </is>
       </c>
-      <c r="AA58" t="inlineStr"/>
+      <c r="AA58" t="inlineStr">
+        <is>
+          <t>webgains</t>
+        </is>
+      </c>
       <c r="AB58" t="inlineStr"/>
       <c r="AC58" t="inlineStr"/>
       <c r="AD58" t="inlineStr"/>
@@ -8574,26 +8578,26 @@
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>Skimbit LTD</t>
+          <t>LINKGAINS PTE.LTD.</t>
         </is>
       </c>
       <c r="B60" s="16" t="n">
-        <v>222</v>
+        <v>235</v>
       </c>
       <c r="C60" s="16" t="n">
-        <v>13.32</v>
+        <v>14.1</v>
       </c>
       <c r="D60" s="16" t="n">
-        <v>4</v>
+        <v>4.23</v>
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>10/03/25 11:13</t>
+          <t>10/02/25 15:28</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>79575</t>
+          <t>79526</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
@@ -8613,17 +8617,17 @@
       </c>
       <c r="J60" t="inlineStr">
         <is>
-          <t>Adidas Campus 00s Camp Noble Maroon, Adidas Samba OG Fox Brown Off White Gum</t>
+          <t>New Balance 204L Mushroom Arid Stone</t>
         </is>
       </c>
       <c r="K60" t="inlineStr">
         <is>
-          <t>39.3 EU - 6.5 US, 39.3 EU - 6.5 US</t>
+          <t>38.5 EU - 6 US</t>
         </is>
       </c>
       <c r="L60" t="inlineStr">
         <is>
-          <t>JQ8349, JR0892</t>
+          <t>U204LMMA</t>
         </is>
       </c>
       <c r="M60" t="inlineStr">
@@ -8647,17 +8651,17 @@
       <c r="S60" t="inlineStr"/>
       <c r="T60" t="inlineStr">
         <is>
-          <t>dianapascual1984@gmail.com</t>
+          <t>lorealc1991@hotmail.com</t>
         </is>
       </c>
       <c r="U60" t="inlineStr">
         <is>
-          <t>Diana</t>
+          <t>Lorena</t>
         </is>
       </c>
       <c r="V60" t="inlineStr">
         <is>
-          <t>Pascual Diaz</t>
+          <t>Cortes alcalde</t>
         </is>
       </c>
       <c r="W60" t="inlineStr"/>
@@ -8673,14 +8677,10 @@
       </c>
       <c r="Z60" t="inlineStr">
         <is>
-          <t>https://www.sequra.com/</t>
-        </is>
-      </c>
-      <c r="AA60" t="inlineStr">
-        <is>
-          <t>webgains</t>
-        </is>
-      </c>
+          <t>Google</t>
+        </is>
+      </c>
+      <c r="AA60" t="inlineStr"/>
       <c r="AB60" t="inlineStr"/>
       <c r="AC60" t="inlineStr"/>
       <c r="AD60" t="inlineStr"/>
@@ -8791,12 +8791,12 @@
       <c r="W61" s="21" t="inlineStr"/>
       <c r="X61" s="21" t="inlineStr">
         <is>
-          <t>Repeat Customer (Order #3)</t>
+          <t>Repeat Customer (Order #4)</t>
         </is>
       </c>
       <c r="Y61" s="21" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="Z61" s="21" t="inlineStr">
@@ -8814,26 +8814,26 @@
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>Webravo SRL</t>
+          <t>Invoke AB</t>
         </is>
       </c>
       <c r="B62" s="16" t="n">
-        <v>45</v>
+        <v>120</v>
       </c>
       <c r="C62" s="16" t="n">
-        <v>2.25</v>
+        <v>7.2</v>
       </c>
       <c r="D62" s="16" t="n">
-        <v>0.68</v>
+        <v>2.16</v>
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>10/02/25 12:21</t>
+          <t>10/01/25 18:12</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>79504</t>
+          <t>79465</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
@@ -8843,27 +8843,27 @@
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>Retail</t>
+          <t>Reventa</t>
         </is>
       </c>
       <c r="I62" s="17" t="inlineStr">
         <is>
-          <t>5%</t>
+          <t>6%</t>
         </is>
       </c>
       <c r="J62" t="inlineStr">
         <is>
-          <t>Pop Mart Labubu The Monsters Big into Energy Series</t>
+          <t>Adidas Samba OG Maroon Off White Gum</t>
         </is>
       </c>
       <c r="K62" t="inlineStr">
         <is>
-          <t>Single Box</t>
+          <t>36.6 EU - 4.5 US</t>
         </is>
       </c>
       <c r="L62" t="inlineStr">
         <is>
-          <t>PPMTBES</t>
+          <t>JR8844</t>
         </is>
       </c>
       <c r="M62" t="inlineStr">
@@ -8887,17 +8887,17 @@
       <c r="S62" t="inlineStr"/>
       <c r="T62" t="inlineStr">
         <is>
-          <t>vicenteignacio.vf@gmail.com</t>
+          <t>ibancerezo0@gmail.com</t>
         </is>
       </c>
       <c r="U62" t="inlineStr">
         <is>
-          <t>Vicente</t>
+          <t>Ana</t>
         </is>
       </c>
       <c r="V62" t="inlineStr">
         <is>
-          <t>Vicente</t>
+          <t>Bolado</t>
         </is>
       </c>
       <c r="W62" t="inlineStr"/>
@@ -8913,24 +8913,12 @@
       </c>
       <c r="Z62" t="inlineStr">
         <is>
-          <t>an unknown source</t>
-        </is>
-      </c>
-      <c r="AA62" t="inlineStr">
-        <is>
-          <t>google</t>
-        </is>
-      </c>
-      <c r="AB62" t="inlineStr">
-        <is>
-          <t>cpc</t>
-        </is>
-      </c>
-      <c r="AC62" t="inlineStr">
-        <is>
-          <t>{campaignname}</t>
-        </is>
-      </c>
+          <t>direct</t>
+        </is>
+      </c>
+      <c r="AA62" t="inlineStr"/>
+      <c r="AB62" t="inlineStr"/>
+      <c r="AC62" t="inlineStr"/>
       <c r="AD62" t="inlineStr"/>
       <c r="AE62" t="inlineStr"/>
       <c r="AF62" t="inlineStr"/>
@@ -8938,26 +8926,26 @@
     <row r="63">
       <c r="A63" s="18" t="inlineStr">
         <is>
-          <t>Invoke AB</t>
+          <t>Webravo SRL</t>
         </is>
       </c>
       <c r="B63" s="19" t="n">
-        <v>120</v>
+        <v>45</v>
       </c>
       <c r="C63" s="19" t="n">
-        <v>7.2</v>
+        <v>2.25</v>
       </c>
       <c r="D63" s="19" t="n">
-        <v>2.16</v>
+        <v>0.68</v>
       </c>
       <c r="E63" s="18" t="inlineStr">
         <is>
-          <t>10/01/25 18:12</t>
+          <t>10/02/25 12:21</t>
         </is>
       </c>
       <c r="F63" s="18" t="inlineStr">
         <is>
-          <t>79465</t>
+          <t>79504</t>
         </is>
       </c>
       <c r="G63" s="18" t="inlineStr">
@@ -8967,27 +8955,27 @@
       </c>
       <c r="H63" s="18" t="inlineStr">
         <is>
-          <t>Reventa</t>
+          <t>Retail</t>
         </is>
       </c>
       <c r="I63" s="20" t="inlineStr">
         <is>
-          <t>6%</t>
+          <t>5%</t>
         </is>
       </c>
       <c r="J63" s="18" t="inlineStr">
         <is>
-          <t>Adidas Samba OG Maroon Off White Gum</t>
+          <t>Pop Mart Labubu The Monsters Big into Energy Series</t>
         </is>
       </c>
       <c r="K63" s="18" t="inlineStr">
         <is>
-          <t>36.6 EU - 4.5 US</t>
+          <t>Single Box</t>
         </is>
       </c>
       <c r="L63" s="18" t="inlineStr">
         <is>
-          <t>JR8844</t>
+          <t>PPMTBES</t>
         </is>
       </c>
       <c r="M63" s="18" t="inlineStr">
@@ -9011,17 +8999,17 @@
       <c r="S63" s="18" t="inlineStr"/>
       <c r="T63" s="18" t="inlineStr">
         <is>
-          <t>ibancerezo0@gmail.com</t>
+          <t>vicenteignacio.vf@gmail.com</t>
         </is>
       </c>
       <c r="U63" s="18" t="inlineStr">
         <is>
-          <t>Ana</t>
+          <t>Vicente</t>
         </is>
       </c>
       <c r="V63" s="18" t="inlineStr">
         <is>
-          <t>Bolado</t>
+          <t>Vicente</t>
         </is>
       </c>
       <c r="W63" s="18" t="inlineStr"/>
@@ -9037,12 +9025,24 @@
       </c>
       <c r="Z63" s="18" t="inlineStr">
         <is>
-          <t>direct</t>
-        </is>
-      </c>
-      <c r="AA63" s="18" t="inlineStr"/>
-      <c r="AB63" s="18" t="inlineStr"/>
-      <c r="AC63" s="18" t="inlineStr"/>
+          <t>an unknown source</t>
+        </is>
+      </c>
+      <c r="AA63" s="18" t="inlineStr">
+        <is>
+          <t>google</t>
+        </is>
+      </c>
+      <c r="AB63" s="18" t="inlineStr">
+        <is>
+          <t>cpc</t>
+        </is>
+      </c>
+      <c r="AC63" s="18" t="inlineStr">
+        <is>
+          <t>{campaignname}</t>
+        </is>
+      </c>
       <c r="AD63" s="18" t="inlineStr"/>
       <c r="AE63" s="18" t="inlineStr"/>
       <c r="AF63" s="18" t="inlineStr"/>
@@ -9238,26 +9238,26 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Invoke AB</t>
+          <t>Shoparize</t>
         </is>
       </c>
       <c r="B2" s="16" t="n">
-        <v>79</v>
+        <v>110</v>
       </c>
       <c r="C2" s="16" t="n">
-        <v>3.95</v>
+        <v>5.5</v>
       </c>
       <c r="D2" s="16" t="n">
-        <v>1.19</v>
+        <v>1.65</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>10/31/25 17:34</t>
+          <t>10/31/25 20:32</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>82052</t>
+          <t>82087</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
@@ -9320,26 +9320,26 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Pashion.dk ApS</t>
+          <t>Invoke AB</t>
         </is>
       </c>
       <c r="B4" s="16" t="n">
-        <v>220</v>
+        <v>79</v>
       </c>
       <c r="C4" s="16" t="n">
-        <v>13.2</v>
+        <v>3.95</v>
       </c>
       <c r="D4" s="16" t="n">
-        <v>3.96</v>
+        <v>1.19</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>10/30/25 15:27</t>
+          <t>10/31/25 17:34</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>81940</t>
+          <t>82052</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
@@ -9349,38 +9349,38 @@
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>Reventa</t>
+          <t>Retail</t>
         </is>
       </c>
       <c r="I4" s="17" t="inlineStr">
         <is>
-          <t>6%</t>
+          <t>5%</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="18" t="inlineStr">
         <is>
-          <t>Shoparize</t>
+          <t>Pashion.dk ApS</t>
         </is>
       </c>
       <c r="B5" s="19" t="n">
-        <v>110</v>
+        <v>72</v>
       </c>
       <c r="C5" s="19" t="n">
-        <v>5.5</v>
+        <v>4.32</v>
       </c>
       <c r="D5" s="19" t="n">
-        <v>1.65</v>
+        <v>1.3</v>
       </c>
       <c r="E5" s="18" t="inlineStr">
         <is>
-          <t>10/31/25 20:32</t>
+          <t>10/30/25 17:45</t>
         </is>
       </c>
       <c r="F5" s="18" t="inlineStr">
         <is>
-          <t>82087</t>
+          <t>81967</t>
         </is>
       </c>
       <c r="G5" s="18" t="inlineStr">
@@ -9390,12 +9390,12 @@
       </c>
       <c r="H5" s="18" t="inlineStr">
         <is>
-          <t>Retail</t>
+          <t>Reventa</t>
         </is>
       </c>
       <c r="I5" s="20" t="inlineStr">
         <is>
-          <t>5%</t>
+          <t>6%</t>
         </is>
       </c>
     </row>
@@ -9406,22 +9406,22 @@
         </is>
       </c>
       <c r="B6" s="16" t="n">
-        <v>72</v>
+        <v>220</v>
       </c>
       <c r="C6" s="16" t="n">
-        <v>4.32</v>
+        <v>13.2</v>
       </c>
       <c r="D6" s="16" t="n">
-        <v>1.3</v>
+        <v>3.96</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>10/30/25 17:45</t>
+          <t>10/30/25 15:27</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>81967</t>
+          <t>81940</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
@@ -9648,26 +9648,26 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Invoke AB</t>
+          <t>Digital Expand</t>
         </is>
       </c>
       <c r="B12" s="16" t="n">
-        <v>170</v>
+        <v>120</v>
       </c>
       <c r="C12" s="16" t="n">
-        <v>8.5</v>
+        <v>7.2</v>
       </c>
       <c r="D12" s="16" t="n">
-        <v>2.55</v>
+        <v>2.16</v>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>10/27/25 18:02</t>
+          <t>10/27/25 16:56</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>81740</t>
+          <t>81727</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
@@ -9677,38 +9677,38 @@
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>Retail</t>
+          <t>Reventa</t>
         </is>
       </c>
       <c r="I12" s="17" t="inlineStr">
         <is>
-          <t>5%</t>
+          <t>6%</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="18" t="inlineStr">
         <is>
-          <t>Purplee Corp</t>
+          <t>Invoke AB</t>
         </is>
       </c>
       <c r="B13" s="19" t="n">
-        <v>82.5</v>
+        <v>170</v>
       </c>
       <c r="C13" s="19" t="n">
-        <v>4.95</v>
+        <v>8.5</v>
       </c>
       <c r="D13" s="19" t="n">
-        <v>1.49</v>
+        <v>2.55</v>
       </c>
       <c r="E13" s="18" t="inlineStr">
         <is>
-          <t>10/28/25 14:36</t>
+          <t>10/27/25 18:02</t>
         </is>
       </c>
       <c r="F13" s="18" t="inlineStr">
         <is>
-          <t>81794</t>
+          <t>81740</t>
         </is>
       </c>
       <c r="G13" s="18" t="inlineStr">
@@ -9718,38 +9718,38 @@
       </c>
       <c r="H13" s="18" t="inlineStr">
         <is>
-          <t>Reventa</t>
+          <t>Retail</t>
         </is>
       </c>
       <c r="I13" s="20" t="inlineStr">
         <is>
-          <t>6%</t>
+          <t>5%</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Digital Expand</t>
+          <t>Purplee Corp</t>
         </is>
       </c>
       <c r="B14" s="16" t="n">
-        <v>120</v>
+        <v>82.5</v>
       </c>
       <c r="C14" s="16" t="n">
-        <v>7.2</v>
+        <v>4.95</v>
       </c>
       <c r="D14" s="16" t="n">
-        <v>2.16</v>
+        <v>1.49</v>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>10/27/25 16:56</t>
+          <t>10/28/25 14:36</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>81727</t>
+          <t>81794</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
@@ -9853,26 +9853,26 @@
     <row r="17">
       <c r="A17" s="18" t="inlineStr">
         <is>
-          <t>Digital Expand</t>
+          <t>Invoke AB</t>
         </is>
       </c>
       <c r="B17" s="19" t="n">
-        <v>90</v>
+        <v>72</v>
       </c>
       <c r="C17" s="19" t="n">
-        <v>5.4</v>
+        <v>4.32</v>
       </c>
       <c r="D17" s="19" t="n">
-        <v>1.62</v>
+        <v>1.3</v>
       </c>
       <c r="E17" s="18" t="inlineStr">
         <is>
-          <t>10/26/25 18:15</t>
+          <t>10/26/25 01:10</t>
         </is>
       </c>
       <c r="F17" s="18" t="inlineStr">
         <is>
-          <t>81633</t>
+          <t>81554</t>
         </is>
       </c>
       <c r="G17" s="18" t="inlineStr">
@@ -9894,26 +9894,26 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Invoke AB</t>
+          <t>Digital Expand</t>
         </is>
       </c>
       <c r="B18" s="16" t="n">
-        <v>72</v>
+        <v>90</v>
       </c>
       <c r="C18" s="16" t="n">
-        <v>4.32</v>
+        <v>5.4</v>
       </c>
       <c r="D18" s="16" t="n">
-        <v>1.3</v>
+        <v>1.62</v>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>10/26/25 01:10</t>
+          <t>10/26/25 18:15</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>81554</t>
+          <t>81633</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
@@ -10058,26 +10058,26 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Skimbit LTD</t>
+          <t>Digital Expand</t>
         </is>
       </c>
       <c r="B22" s="16" t="n">
-        <v>102</v>
+        <v>84.5</v>
       </c>
       <c r="C22" s="16" t="n">
-        <v>6.12</v>
+        <v>5.07</v>
       </c>
       <c r="D22" s="16" t="n">
-        <v>1.84</v>
+        <v>1.52</v>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>10/23/25 22:24</t>
+          <t>10/22/25 18:06</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>81350</t>
+          <t>81238</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
@@ -10099,26 +10099,26 @@
     <row r="23">
       <c r="A23" s="18" t="inlineStr">
         <is>
-          <t>Digital Expand</t>
+          <t>BlueVision Interactive Limited</t>
         </is>
       </c>
       <c r="B23" s="19" t="n">
-        <v>110</v>
+        <v>314.9</v>
       </c>
       <c r="C23" s="19" t="n">
-        <v>5.5</v>
+        <v>15.75</v>
       </c>
       <c r="D23" s="19" t="n">
-        <v>1.65</v>
+        <v>4.72</v>
       </c>
       <c r="E23" s="18" t="inlineStr">
         <is>
-          <t>10/22/25 18:00</t>
+          <t>10/22/25 10:59</t>
         </is>
       </c>
       <c r="F23" s="18" t="inlineStr">
         <is>
-          <t>81235</t>
+          <t>81182</t>
         </is>
       </c>
       <c r="G23" s="18" t="inlineStr">
@@ -10140,26 +10140,26 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Digital Expand</t>
+          <t>Skimbit LTD</t>
         </is>
       </c>
       <c r="B24" s="16" t="n">
-        <v>84.5</v>
+        <v>102</v>
       </c>
       <c r="C24" s="16" t="n">
-        <v>5.07</v>
+        <v>6.12</v>
       </c>
       <c r="D24" s="16" t="n">
-        <v>1.52</v>
+        <v>1.84</v>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>10/22/25 18:06</t>
+          <t>10/23/25 22:24</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>81238</t>
+          <t>81350</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
@@ -10181,26 +10181,26 @@
     <row r="25">
       <c r="A25" s="18" t="inlineStr">
         <is>
-          <t>BlueVision Interactive Limited</t>
+          <t>Digital Expand</t>
         </is>
       </c>
       <c r="B25" s="19" t="n">
-        <v>314.9</v>
+        <v>110</v>
       </c>
       <c r="C25" s="19" t="n">
-        <v>15.75</v>
+        <v>5.5</v>
       </c>
       <c r="D25" s="19" t="n">
-        <v>4.72</v>
+        <v>1.65</v>
       </c>
       <c r="E25" s="18" t="inlineStr">
         <is>
-          <t>10/22/25 10:59</t>
+          <t>10/22/25 18:00</t>
         </is>
       </c>
       <c r="F25" s="18" t="inlineStr">
         <is>
-          <t>81182</t>
+          <t>81235</t>
         </is>
       </c>
       <c r="G25" s="18" t="inlineStr">
@@ -10222,31 +10222,31 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Deal Savings LLC</t>
+          <t>Skimbit LTD</t>
         </is>
       </c>
       <c r="B26" s="16" t="n">
-        <v>102</v>
+        <v>150</v>
       </c>
       <c r="C26" s="16" t="n">
-        <v>6.12</v>
+        <v>9</v>
       </c>
       <c r="D26" s="16" t="n">
-        <v>1.84</v>
+        <v>2.7</v>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>10/20/25 10:11</t>
+          <t>10/21/25 23:07</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>81037</t>
+          <t>81173</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>ES</t>
+          <t>FR</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
@@ -10263,31 +10263,31 @@
     <row r="27">
       <c r="A27" s="18" t="inlineStr">
         <is>
-          <t>Skimbit LTD</t>
+          <t>Deal Savings LLC</t>
         </is>
       </c>
       <c r="B27" s="19" t="n">
-        <v>150</v>
+        <v>102</v>
       </c>
       <c r="C27" s="19" t="n">
-        <v>9</v>
+        <v>6.12</v>
       </c>
       <c r="D27" s="19" t="n">
-        <v>2.7</v>
+        <v>1.84</v>
       </c>
       <c r="E27" s="18" t="inlineStr">
         <is>
-          <t>10/21/25 23:07</t>
+          <t>10/20/25 10:11</t>
         </is>
       </c>
       <c r="F27" s="18" t="inlineStr">
         <is>
-          <t>81173</t>
+          <t>81037</t>
         </is>
       </c>
       <c r="G27" s="18" t="inlineStr">
         <is>
-          <t>FR</t>
+          <t>ES</t>
         </is>
       </c>
       <c r="H27" s="18" t="inlineStr">
@@ -10304,26 +10304,26 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Shoparize</t>
+          <t>Invoke AB</t>
         </is>
       </c>
       <c r="B28" s="16" t="n">
-        <v>100</v>
+        <v>96</v>
       </c>
       <c r="C28" s="16" t="n">
-        <v>5</v>
+        <v>4.8</v>
       </c>
       <c r="D28" s="16" t="n">
-        <v>1.5</v>
+        <v>1.44</v>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>10/19/25 21:03</t>
+          <t>10/19/25 18:19</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>81033</t>
+          <t>81015</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
@@ -10345,31 +10345,31 @@
     <row r="29">
       <c r="A29" s="18" t="inlineStr">
         <is>
-          <t>Invoke AB</t>
+          <t>LINKGAINS PTE.LTD.</t>
         </is>
       </c>
       <c r="B29" s="19" t="n">
-        <v>96</v>
+        <v>185</v>
       </c>
       <c r="C29" s="19" t="n">
-        <v>4.8</v>
+        <v>9.6</v>
       </c>
       <c r="D29" s="19" t="n">
-        <v>1.44</v>
+        <v>2.88</v>
       </c>
       <c r="E29" s="18" t="inlineStr">
         <is>
-          <t>10/19/25 18:19</t>
+          <t>10/19/25 09:51</t>
         </is>
       </c>
       <c r="F29" s="18" t="inlineStr">
         <is>
-          <t>81015</t>
+          <t>80931</t>
         </is>
       </c>
       <c r="G29" s="18" t="inlineStr">
         <is>
-          <t>ES</t>
+          <t>FR</t>
         </is>
       </c>
       <c r="H29" s="18" t="inlineStr">
@@ -10386,31 +10386,31 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>LINKGAINS PTE.LTD.</t>
+          <t>Shoparize</t>
         </is>
       </c>
       <c r="B30" s="16" t="n">
-        <v>185</v>
+        <v>100</v>
       </c>
       <c r="C30" s="16" t="n">
-        <v>9.6</v>
+        <v>5</v>
       </c>
       <c r="D30" s="16" t="n">
-        <v>2.88</v>
+        <v>1.5</v>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>10/19/25 09:51</t>
+          <t>10/19/25 21:03</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>80931</t>
+          <t>81033</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>FR</t>
+          <t>ES</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
@@ -10427,26 +10427,26 @@
     <row r="31">
       <c r="A31" s="18" t="inlineStr">
         <is>
-          <t>LINKGAINS PTE.LTD.</t>
+          <t>BlueVision Interactive Limited</t>
         </is>
       </c>
       <c r="B31" s="19" t="n">
-        <v>89</v>
+        <v>99</v>
       </c>
       <c r="C31" s="19" t="n">
-        <v>5.34</v>
+        <v>5.94</v>
       </c>
       <c r="D31" s="19" t="n">
-        <v>1.6</v>
+        <v>1.78</v>
       </c>
       <c r="E31" s="18" t="inlineStr">
         <is>
-          <t>10/18/25 16:27</t>
+          <t>10/19/25 00:09</t>
         </is>
       </c>
       <c r="F31" s="18" t="inlineStr">
         <is>
-          <t>80872</t>
+          <t>80926</t>
         </is>
       </c>
       <c r="G31" s="18" t="inlineStr">
@@ -10468,26 +10468,26 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>BlueVision Interactive Limited</t>
+          <t>LINKGAINS PTE.LTD.</t>
         </is>
       </c>
       <c r="B32" s="16" t="n">
-        <v>99</v>
+        <v>89</v>
       </c>
       <c r="C32" s="16" t="n">
-        <v>5.94</v>
+        <v>5.34</v>
       </c>
       <c r="D32" s="16" t="n">
-        <v>1.78</v>
+        <v>1.6</v>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>10/19/25 00:09</t>
+          <t>10/18/25 16:27</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>80926</t>
+          <t>80872</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
@@ -10591,26 +10591,26 @@
     <row r="35">
       <c r="A35" s="18" t="inlineStr">
         <is>
-          <t>Skimbit LTD</t>
+          <t>BlueVision Interactive Limited</t>
         </is>
       </c>
       <c r="B35" s="19" t="n">
-        <v>120</v>
+        <v>79</v>
       </c>
       <c r="C35" s="19" t="n">
-        <v>7.2</v>
+        <v>3.95</v>
       </c>
       <c r="D35" s="19" t="n">
-        <v>2.16</v>
+        <v>1.19</v>
       </c>
       <c r="E35" s="18" t="inlineStr">
         <is>
-          <t>10/14/25 16:56</t>
+          <t>10/14/25 21:47</t>
         </is>
       </c>
       <c r="F35" s="18" t="inlineStr">
         <is>
-          <t>80572</t>
+          <t>80603</t>
         </is>
       </c>
       <c r="G35" s="18" t="inlineStr">
@@ -10620,12 +10620,12 @@
       </c>
       <c r="H35" s="18" t="inlineStr">
         <is>
-          <t>Reventa</t>
+          <t>Retail</t>
         </is>
       </c>
       <c r="I35" s="20" t="inlineStr">
         <is>
-          <t>6%</t>
+          <t>5%</t>
         </is>
       </c>
     </row>
@@ -10636,22 +10636,22 @@
         </is>
       </c>
       <c r="B36" s="16" t="n">
-        <v>102</v>
+        <v>120</v>
       </c>
       <c r="C36" s="16" t="n">
-        <v>6.12</v>
+        <v>7.2</v>
       </c>
       <c r="D36" s="16" t="n">
-        <v>1.84</v>
+        <v>2.16</v>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>10/14/25 18:53</t>
+          <t>10/14/25 16:56</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>80587</t>
+          <t>80572</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
@@ -10673,26 +10673,26 @@
     <row r="37">
       <c r="A37" s="18" t="inlineStr">
         <is>
-          <t>BlueVision Interactive Limited</t>
+          <t>Skimbit LTD</t>
         </is>
       </c>
       <c r="B37" s="19" t="n">
-        <v>79</v>
+        <v>102</v>
       </c>
       <c r="C37" s="19" t="n">
-        <v>3.95</v>
+        <v>6.12</v>
       </c>
       <c r="D37" s="19" t="n">
-        <v>1.19</v>
+        <v>1.84</v>
       </c>
       <c r="E37" s="18" t="inlineStr">
         <is>
-          <t>10/14/25 21:47</t>
+          <t>10/14/25 18:53</t>
         </is>
       </c>
       <c r="F37" s="18" t="inlineStr">
         <is>
-          <t>80603</t>
+          <t>80587</t>
         </is>
       </c>
       <c r="G37" s="18" t="inlineStr">
@@ -10702,12 +10702,12 @@
       </c>
       <c r="H37" s="18" t="inlineStr">
         <is>
-          <t>Retail</t>
+          <t>Reventa</t>
         </is>
       </c>
       <c r="I37" s="20" t="inlineStr">
         <is>
-          <t>5%</t>
+          <t>6%</t>
         </is>
       </c>
     </row>
@@ -10878,26 +10878,26 @@
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>AFILIZA</t>
+          <t>Skimbit LTD</t>
         </is>
       </c>
       <c r="B42" s="16" t="n">
-        <v>96</v>
+        <v>270</v>
       </c>
       <c r="C42" s="16" t="n">
-        <v>4.8</v>
+        <v>13.5</v>
       </c>
       <c r="D42" s="16" t="n">
-        <v>1.44</v>
+        <v>4.05</v>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>10/12/25 14:51</t>
+          <t>10/12/25 13:04</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>80384</t>
+          <t>80372</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
@@ -10919,26 +10919,26 @@
     <row r="43">
       <c r="A43" s="18" t="inlineStr">
         <is>
-          <t>Skimbit LTD</t>
+          <t>AFILIZA</t>
         </is>
       </c>
       <c r="B43" s="19" t="n">
-        <v>270</v>
+        <v>96</v>
       </c>
       <c r="C43" s="19" t="n">
-        <v>13.5</v>
+        <v>4.8</v>
       </c>
       <c r="D43" s="19" t="n">
-        <v>4.05</v>
+        <v>1.44</v>
       </c>
       <c r="E43" s="18" t="inlineStr">
         <is>
-          <t>10/12/25 13:04</t>
+          <t>10/12/25 14:51</t>
         </is>
       </c>
       <c r="F43" s="18" t="inlineStr">
         <is>
-          <t>80372</t>
+          <t>80384</t>
         </is>
       </c>
       <c r="G43" s="18" t="inlineStr">
@@ -11046,22 +11046,22 @@
         </is>
       </c>
       <c r="B46" s="16" t="n">
-        <v>130</v>
+        <v>110</v>
       </c>
       <c r="C46" s="16" t="n">
-        <v>6.5</v>
+        <v>5.5</v>
       </c>
       <c r="D46" s="16" t="n">
-        <v>1.95</v>
+        <v>1.65</v>
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>10/09/25 08:34</t>
+          <t>10/10/25 18:32</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>80075</t>
+          <t>80196</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
@@ -11128,22 +11128,22 @@
         </is>
       </c>
       <c r="B48" s="16" t="n">
-        <v>110</v>
+        <v>130</v>
       </c>
       <c r="C48" s="16" t="n">
-        <v>5.5</v>
+        <v>6.5</v>
       </c>
       <c r="D48" s="16" t="n">
-        <v>1.65</v>
+        <v>1.95</v>
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>10/10/25 18:32</t>
+          <t>10/09/25 08:34</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>80196</t>
+          <t>80075</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
@@ -11288,26 +11288,26 @@
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>Pashion.dk ApS</t>
+          <t>Skimbit LTD</t>
         </is>
       </c>
       <c r="B52" s="16" t="n">
-        <v>450</v>
+        <v>250</v>
       </c>
       <c r="C52" s="16" t="n">
-        <v>22.5</v>
+        <v>15</v>
       </c>
       <c r="D52" s="16" t="n">
-        <v>6.75</v>
+        <v>4.5</v>
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>10/05/25 12:16</t>
+          <t>10/05/25 01:11</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>79766</t>
+          <t>79760</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
@@ -11317,38 +11317,38 @@
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>Retail</t>
+          <t>Reventa</t>
         </is>
       </c>
       <c r="I52" s="17" t="inlineStr">
         <is>
-          <t>5%</t>
+          <t>6%</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" s="18" t="inlineStr">
         <is>
-          <t>Skimbit LTD</t>
+          <t>AFILIZA</t>
         </is>
       </c>
       <c r="B53" s="19" t="n">
-        <v>250</v>
+        <v>110</v>
       </c>
       <c r="C53" s="19" t="n">
-        <v>15</v>
+        <v>5.5</v>
       </c>
       <c r="D53" s="19" t="n">
-        <v>4.5</v>
+        <v>1.65</v>
       </c>
       <c r="E53" s="18" t="inlineStr">
         <is>
-          <t>10/05/25 01:11</t>
+          <t>10/04/25 19:13</t>
         </is>
       </c>
       <c r="F53" s="18" t="inlineStr">
         <is>
-          <t>79760</t>
+          <t>79730</t>
         </is>
       </c>
       <c r="G53" s="18" t="inlineStr">
@@ -11358,38 +11358,38 @@
       </c>
       <c r="H53" s="18" t="inlineStr">
         <is>
-          <t>Reventa</t>
+          <t>Retail</t>
         </is>
       </c>
       <c r="I53" s="20" t="inlineStr">
         <is>
-          <t>6%</t>
+          <t>5%</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>Purplee Corp</t>
+          <t>Pashion.dk ApS</t>
         </is>
       </c>
       <c r="B54" s="16" t="n">
-        <v>89</v>
+        <v>450</v>
       </c>
       <c r="C54" s="16" t="n">
-        <v>5.34</v>
+        <v>22.5</v>
       </c>
       <c r="D54" s="16" t="n">
-        <v>1.6</v>
+        <v>6.75</v>
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>10/04/25 17:01</t>
+          <t>10/05/25 12:16</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>79706</t>
+          <t>79766</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
@@ -11399,38 +11399,38 @@
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>Reventa</t>
+          <t>Retail</t>
         </is>
       </c>
       <c r="I54" s="17" t="inlineStr">
         <is>
-          <t>6%</t>
+          <t>5%</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" s="18" t="inlineStr">
         <is>
-          <t>AFILIZA</t>
+          <t>Purplee Corp</t>
         </is>
       </c>
       <c r="B55" s="19" t="n">
-        <v>110</v>
+        <v>89</v>
       </c>
       <c r="C55" s="19" t="n">
-        <v>5.5</v>
+        <v>5.34</v>
       </c>
       <c r="D55" s="19" t="n">
-        <v>1.65</v>
+        <v>1.6</v>
       </c>
       <c r="E55" s="18" t="inlineStr">
         <is>
-          <t>10/04/25 19:13</t>
+          <t>10/04/25 17:01</t>
         </is>
       </c>
       <c r="F55" s="18" t="inlineStr">
         <is>
-          <t>79730</t>
+          <t>79706</t>
         </is>
       </c>
       <c r="G55" s="18" t="inlineStr">
@@ -11440,12 +11440,12 @@
       </c>
       <c r="H55" s="18" t="inlineStr">
         <is>
-          <t>Retail</t>
+          <t>Reventa</t>
         </is>
       </c>
       <c r="I55" s="20" t="inlineStr">
         <is>
-          <t>5%</t>
+          <t>6%</t>
         </is>
       </c>
     </row>
@@ -11493,26 +11493,26 @@
     <row r="57">
       <c r="A57" s="18" t="inlineStr">
         <is>
-          <t>Pashion.dk ApS</t>
+          <t>Skimbit LTD</t>
         </is>
       </c>
       <c r="B57" s="19" t="n">
-        <v>90</v>
+        <v>222</v>
       </c>
       <c r="C57" s="19" t="n">
-        <v>4.5</v>
+        <v>13.32</v>
       </c>
       <c r="D57" s="19" t="n">
-        <v>1.35</v>
+        <v>4</v>
       </c>
       <c r="E57" s="18" t="inlineStr">
         <is>
-          <t>10/04/25 12:10</t>
+          <t>10/03/25 11:13</t>
         </is>
       </c>
       <c r="F57" s="18" t="inlineStr">
         <is>
-          <t>79651</t>
+          <t>79575</t>
         </is>
       </c>
       <c r="G57" s="18" t="inlineStr">
@@ -11522,38 +11522,38 @@
       </c>
       <c r="H57" s="18" t="inlineStr">
         <is>
-          <t>Retail</t>
+          <t>Reventa</t>
         </is>
       </c>
       <c r="I57" s="20" t="inlineStr">
         <is>
-          <t>5%</t>
+          <t>6%</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>LINKGAINS PTE.LTD.</t>
+          <t>Pashion.dk ApS</t>
         </is>
       </c>
       <c r="B58" s="16" t="n">
-        <v>235</v>
+        <v>90</v>
       </c>
       <c r="C58" s="16" t="n">
-        <v>14.1</v>
+        <v>4.5</v>
       </c>
       <c r="D58" s="16" t="n">
-        <v>4.23</v>
+        <v>1.35</v>
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>10/02/25 15:28</t>
+          <t>10/04/25 12:10</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>79526</t>
+          <t>79651</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
@@ -11563,12 +11563,12 @@
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>Reventa</t>
+          <t>Retail</t>
         </is>
       </c>
       <c r="I58" s="17" t="inlineStr">
         <is>
-          <t>6%</t>
+          <t>5%</t>
         </is>
       </c>
     </row>
@@ -11616,26 +11616,26 @@
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>Skimbit LTD</t>
+          <t>LINKGAINS PTE.LTD.</t>
         </is>
       </c>
       <c r="B60" s="16" t="n">
-        <v>222</v>
+        <v>235</v>
       </c>
       <c r="C60" s="16" t="n">
-        <v>13.32</v>
+        <v>14.1</v>
       </c>
       <c r="D60" s="16" t="n">
-        <v>4</v>
+        <v>4.23</v>
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>10/03/25 11:13</t>
+          <t>10/02/25 15:28</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>79575</t>
+          <t>79526</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
@@ -11698,26 +11698,26 @@
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>Webravo SRL</t>
+          <t>Invoke AB</t>
         </is>
       </c>
       <c r="B62" s="16" t="n">
-        <v>45</v>
+        <v>120</v>
       </c>
       <c r="C62" s="16" t="n">
-        <v>2.25</v>
+        <v>7.2</v>
       </c>
       <c r="D62" s="16" t="n">
-        <v>0.68</v>
+        <v>2.16</v>
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>10/02/25 12:21</t>
+          <t>10/01/25 18:12</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>79504</t>
+          <t>79465</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
@@ -11727,38 +11727,38 @@
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>Retail</t>
+          <t>Reventa</t>
         </is>
       </c>
       <c r="I62" s="17" t="inlineStr">
         <is>
-          <t>5%</t>
+          <t>6%</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" s="18" t="inlineStr">
         <is>
-          <t>Invoke AB</t>
+          <t>Webravo SRL</t>
         </is>
       </c>
       <c r="B63" s="19" t="n">
-        <v>120</v>
+        <v>45</v>
       </c>
       <c r="C63" s="19" t="n">
-        <v>7.2</v>
+        <v>2.25</v>
       </c>
       <c r="D63" s="19" t="n">
-        <v>2.16</v>
+        <v>0.68</v>
       </c>
       <c r="E63" s="18" t="inlineStr">
         <is>
-          <t>10/01/25 18:12</t>
+          <t>10/02/25 12:21</t>
         </is>
       </c>
       <c r="F63" s="18" t="inlineStr">
         <is>
-          <t>79465</t>
+          <t>79504</t>
         </is>
       </c>
       <c r="G63" s="18" t="inlineStr">
@@ -11768,12 +11768,12 @@
       </c>
       <c r="H63" s="18" t="inlineStr">
         <is>
-          <t>Reventa</t>
+          <t>Retail</t>
         </is>
       </c>
       <c r="I63" s="20" t="inlineStr">
         <is>
-          <t>6%</t>
+          <t>5%</t>
         </is>
       </c>
     </row>
